--- a/research/traditional_assets/database/data/south_africa/south_africa_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_farming_agriculture.xlsx
@@ -588,37 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0416</v>
-      </c>
-      <c r="E2">
-        <v>0.192</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="G2">
-        <v>0.1663157894736842</v>
+        <v>0.01596153846153846</v>
       </c>
       <c r="H2">
-        <v>0.1663157894736842</v>
+        <v>0.01596153846153846</v>
       </c>
       <c r="I2">
-        <v>-0.005631428258056693</v>
+        <v>-0.06730769230769232</v>
       </c>
       <c r="J2">
-        <v>-0.005631428258056693</v>
+        <v>-0.06730769230769232</v>
       </c>
       <c r="K2">
-        <v>1.85</v>
+        <v>-6.2</v>
       </c>
       <c r="L2">
-        <v>0.0486842105263158</v>
+        <v>-0.1703296703296703</v>
       </c>
       <c r="M2">
-        <v>0.39</v>
+        <v>0.012</v>
       </c>
       <c r="N2">
-        <v>0.01270358306188925</v>
+        <v>0.0004562737642585551</v>
       </c>
       <c r="O2">
-        <v>0.2108108108108108</v>
+        <v>-0.001935483870967742</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,82 +624,82 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.39</v>
+        <v>0.012</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>3.16</v>
+        <v>6.5</v>
       </c>
       <c r="V2">
-        <v>0.1029315960912052</v>
+        <v>0.247148288973384</v>
       </c>
       <c r="W2">
-        <v>0.02677279305354559</v>
+        <v>-0.09702660406885759</v>
       </c>
       <c r="X2">
-        <v>0.1570011892407265</v>
+        <v>0.1342908981143513</v>
       </c>
       <c r="Y2">
-        <v>-0.1302283961871809</v>
+        <v>-0.2313175021832089</v>
       </c>
       <c r="Z2">
-        <v>0.4291846881406551</v>
+        <v>0.4240447343895619</v>
       </c>
       <c r="AA2">
-        <v>-0.002416922780720534</v>
+        <v>-0.02854147250698975</v>
       </c>
       <c r="AB2">
-        <v>0.1174681832905259</v>
+        <v>0.0969672865287729</v>
       </c>
       <c r="AC2">
-        <v>-0.1198851060712464</v>
+        <v>-0.1255087590357626</v>
       </c>
       <c r="AD2">
-        <v>25.1</v>
+        <v>28.9</v>
       </c>
       <c r="AE2">
-        <v>0.3599713690307717</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>25.45997136903077</v>
+        <v>28.9</v>
       </c>
       <c r="AG2">
-        <v>22.29997136903077</v>
+        <v>22.4</v>
       </c>
       <c r="AH2">
-        <v>0.4533472996581794</v>
+        <v>0.5235507246376812</v>
       </c>
       <c r="AI2">
-        <v>0.2732930355697216</v>
+        <v>0.3302857142857143</v>
       </c>
       <c r="AJ2">
-        <v>0.4207544040686258</v>
+        <v>0.459958932238193</v>
       </c>
       <c r="AK2">
-        <v>0.2477775384793539</v>
+        <v>0.2765432098765432</v>
       </c>
       <c r="AL2">
-        <v>1.54</v>
+        <v>3.01</v>
       </c>
       <c r="AM2">
-        <v>1.153</v>
+        <v>2.661</v>
       </c>
       <c r="AN2">
-        <v>8.74869292436389</v>
+        <v>5.008665511265165</v>
       </c>
       <c r="AO2">
-        <v>-0.1435064935064935</v>
+        <v>-0.8139534883720931</v>
       </c>
       <c r="AP2">
-        <v>7.772733136643698</v>
+        <v>3.882149046793761</v>
       </c>
       <c r="AQ2">
-        <v>-0.191673894189072</v>
+        <v>-0.9207065013152952</v>
       </c>
     </row>
     <row r="3">
@@ -722,37 +719,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0416</v>
-      </c>
-      <c r="E3">
-        <v>0.192</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="G3">
-        <v>0.1663157894736842</v>
+        <v>0.01596153846153846</v>
       </c>
       <c r="H3">
-        <v>0.1663157894736842</v>
+        <v>0.01596153846153846</v>
       </c>
       <c r="I3">
-        <v>-0.005631428258056693</v>
+        <v>-0.06730769230769232</v>
       </c>
       <c r="J3">
-        <v>-0.005631428258056693</v>
+        <v>-0.06730769230769232</v>
       </c>
       <c r="K3">
-        <v>1.85</v>
+        <v>-6.2</v>
       </c>
       <c r="L3">
-        <v>0.0486842105263158</v>
+        <v>-0.1703296703296703</v>
       </c>
       <c r="M3">
-        <v>0.39</v>
+        <v>0.012</v>
       </c>
       <c r="N3">
-        <v>0.01270358306188925</v>
+        <v>0.0004562737642585551</v>
       </c>
       <c r="O3">
-        <v>0.2108108108108108</v>
+        <v>-0.001935483870967742</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -761,82 +755,82 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>0.39</v>
+        <v>0.012</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>3.16</v>
+        <v>6.5</v>
       </c>
       <c r="V3">
-        <v>0.1029315960912052</v>
+        <v>0.247148288973384</v>
       </c>
       <c r="W3">
-        <v>0.02677279305354559</v>
+        <v>-0.09702660406885759</v>
       </c>
       <c r="X3">
-        <v>0.1570011892407265</v>
+        <v>0.1342908981143513</v>
       </c>
       <c r="Y3">
-        <v>-0.1302283961871809</v>
+        <v>-0.2313175021832089</v>
       </c>
       <c r="Z3">
-        <v>0.4291846881406551</v>
+        <v>0.4240447343895619</v>
       </c>
       <c r="AA3">
-        <v>-0.002416922780720534</v>
+        <v>-0.02854147250698975</v>
       </c>
       <c r="AB3">
-        <v>0.1174681832905259</v>
+        <v>0.0969672865287729</v>
       </c>
       <c r="AC3">
-        <v>-0.1198851060712464</v>
+        <v>-0.1255087590357626</v>
       </c>
       <c r="AD3">
-        <v>25.1</v>
+        <v>28.9</v>
       </c>
       <c r="AE3">
-        <v>0.3599713690307717</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>25.45997136903077</v>
+        <v>28.9</v>
       </c>
       <c r="AG3">
-        <v>22.29997136903077</v>
+        <v>22.4</v>
       </c>
       <c r="AH3">
-        <v>0.4533472996581794</v>
+        <v>0.5235507246376812</v>
       </c>
       <c r="AI3">
-        <v>0.2732930355697216</v>
+        <v>0.3302857142857143</v>
       </c>
       <c r="AJ3">
-        <v>0.4207544040686258</v>
+        <v>0.459958932238193</v>
       </c>
       <c r="AK3">
-        <v>0.2477775384793539</v>
+        <v>0.2765432098765432</v>
       </c>
       <c r="AL3">
-        <v>1.54</v>
+        <v>3.01</v>
       </c>
       <c r="AM3">
-        <v>1.153</v>
+        <v>2.661</v>
       </c>
       <c r="AN3">
-        <v>8.74869292436389</v>
+        <v>5.008665511265165</v>
       </c>
       <c r="AO3">
-        <v>-0.1435064935064935</v>
+        <v>-0.8139534883720931</v>
       </c>
       <c r="AP3">
-        <v>7.772733136643698</v>
+        <v>3.882149046793761</v>
       </c>
       <c r="AQ3">
-        <v>-0.191673894189072</v>
+        <v>-0.9207065013152952</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_africa/south_africa_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_farming_agriculture.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09494231283911345</v>
+        <v>0.09471881859444783</v>
       </c>
       <c r="C2">
-        <v>48.89138096467262</v>
+        <v>48.47769768495166</v>
       </c>
       <c r="D2">
-        <v>37.89138096467262</v>
+        <v>37.95969768495166</v>
       </c>
       <c r="E2">
-        <v>-22.8</v>
+        <v>-22.318</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.482</v>
       </c>
       <c r="G2">
         <v>11</v>
@@ -1451,28 +1451,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0242446</v>
       </c>
       <c r="N2">
-        <v>7.974999999999999</v>
+        <v>7.950755399999998</v>
       </c>
       <c r="O2">
-        <v>2.15325</v>
+        <v>2.146703958</v>
       </c>
       <c r="P2">
-        <v>5.821749999999999</v>
+        <v>5.804051441999999</v>
       </c>
       <c r="Q2">
-        <v>9.521749999999999</v>
+        <v>9.504051441999998</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09494231283911345</v>
+        <v>0.09530467534792711</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.59305325452791</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>328.9392277043135</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09471881859444783</v>
+        <v>0.09449532434978225</v>
       </c>
       <c r="C3">
-        <v>48.47769768495166</v>
+        <v>48.06426119508566</v>
       </c>
       <c r="D3">
-        <v>37.95969768495166</v>
+        <v>38.02826119508566</v>
       </c>
       <c r="E3">
-        <v>-22.318</v>
+        <v>-21.836</v>
       </c>
       <c r="F3">
-        <v>0.482</v>
+        <v>0.9640000000000001</v>
       </c>
       <c r="G3">
         <v>11</v>
@@ -1533,28 +1533,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M3">
-        <v>0.0242446</v>
+        <v>0.0484892</v>
       </c>
       <c r="N3">
-        <v>7.950755399999998</v>
+        <v>7.926510799999999</v>
       </c>
       <c r="O3">
-        <v>2.146703958</v>
+        <v>2.140157916</v>
       </c>
       <c r="P3">
-        <v>5.804051441999999</v>
+        <v>5.786352883999999</v>
       </c>
       <c r="Q3">
-        <v>9.504051441999998</v>
+        <v>9.486352883999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09530467534792711</v>
+        <v>0.09567443300998188</v>
       </c>
       <c r="T3">
-        <v>0.59305325452791</v>
+        <v>0.5974828560418484</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>328.9392277043135</v>
+        <v>164.4696138521567</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09449532434978225</v>
+        <v>0.09427183010511662</v>
       </c>
       <c r="C4">
-        <v>48.06426119508566</v>
+        <v>47.65107283476365</v>
       </c>
       <c r="D4">
-        <v>38.02826119508566</v>
+        <v>38.09707283476365</v>
       </c>
       <c r="E4">
-        <v>-21.836</v>
+        <v>-21.354</v>
       </c>
       <c r="F4">
-        <v>0.9640000000000001</v>
+        <v>1.446</v>
       </c>
       <c r="G4">
         <v>11</v>
@@ -1615,28 +1615,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M4">
-        <v>0.0484892</v>
+        <v>0.07273379999999999</v>
       </c>
       <c r="N4">
-        <v>7.926510799999999</v>
+        <v>7.902266199999999</v>
       </c>
       <c r="O4">
-        <v>2.140157916</v>
+        <v>2.133611874</v>
       </c>
       <c r="P4">
-        <v>5.786352883999999</v>
+        <v>5.768654325999999</v>
       </c>
       <c r="Q4">
-        <v>9.486352883999999</v>
+        <v>9.468654325999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09567443300998188</v>
+        <v>0.09605181454135735</v>
       </c>
       <c r="T4">
-        <v>0.5974828560418484</v>
+        <v>0.6020037895457648</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>164.4696138521567</v>
+        <v>109.6464092347712</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09427183010511662</v>
+        <v>0.09404833586045103</v>
       </c>
       <c r="C5">
-        <v>47.65107283476365</v>
+        <v>47.23813395338881</v>
       </c>
       <c r="D5">
-        <v>38.09707283476365</v>
+        <v>38.16613395338881</v>
       </c>
       <c r="E5">
-        <v>-21.354</v>
+        <v>-20.872</v>
       </c>
       <c r="F5">
-        <v>1.446</v>
+        <v>1.928</v>
       </c>
       <c r="G5">
         <v>11</v>
@@ -1697,28 +1697,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M5">
-        <v>0.07273379999999999</v>
+        <v>0.09697840000000001</v>
       </c>
       <c r="N5">
-        <v>7.902266199999999</v>
+        <v>7.878021599999999</v>
       </c>
       <c r="O5">
-        <v>2.133611874</v>
+        <v>2.127065832</v>
       </c>
       <c r="P5">
-        <v>5.768654325999999</v>
+        <v>5.750955767999999</v>
       </c>
       <c r="Q5">
-        <v>9.468654325999999</v>
+        <v>9.450955768</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09605181454135735</v>
+        <v>0.09643705818796983</v>
       </c>
       <c r="T5">
-        <v>0.6020037895457648</v>
+        <v>0.6066189091643464</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>109.6464092347712</v>
+        <v>82.23480692607836</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09404833586045103</v>
+        <v>0.0938248416157854</v>
       </c>
       <c r="C6">
-        <v>47.23813395338881</v>
+        <v>46.82544591016672</v>
       </c>
       <c r="D6">
-        <v>38.16613395338881</v>
+        <v>38.23544591016672</v>
       </c>
       <c r="E6">
-        <v>-20.872</v>
+        <v>-20.39</v>
       </c>
       <c r="F6">
-        <v>1.928</v>
+        <v>2.41</v>
       </c>
       <c r="G6">
         <v>11</v>
@@ -1779,28 +1779,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M6">
-        <v>0.09697840000000001</v>
+        <v>0.121223</v>
       </c>
       <c r="N6">
-        <v>7.878021599999999</v>
+        <v>7.853776999999999</v>
       </c>
       <c r="O6">
-        <v>2.127065832</v>
+        <v>2.12051979</v>
       </c>
       <c r="P6">
-        <v>5.750955767999999</v>
+        <v>5.73325721</v>
       </c>
       <c r="Q6">
-        <v>9.450955768</v>
+        <v>9.433257210000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09643705818796983</v>
+        <v>0.09683041222714253</v>
       </c>
       <c r="T6">
-        <v>0.6066189091643464</v>
+        <v>0.6113311891959504</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>82.23480692607836</v>
+        <v>65.7878455408627</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0938248416157854</v>
+        <v>0.09360134737111982</v>
       </c>
       <c r="C7">
-        <v>46.82544591016672</v>
+        <v>46.4130100741945</v>
       </c>
       <c r="D7">
-        <v>38.23544591016672</v>
+        <v>38.3050100741945</v>
       </c>
       <c r="E7">
-        <v>-20.39</v>
+        <v>-19.908</v>
       </c>
       <c r="F7">
-        <v>2.41</v>
+        <v>2.892</v>
       </c>
       <c r="G7">
         <v>11</v>
@@ -1861,28 +1861,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M7">
-        <v>0.121223</v>
+        <v>0.1454676</v>
       </c>
       <c r="N7">
-        <v>7.853776999999999</v>
+        <v>7.829532399999999</v>
       </c>
       <c r="O7">
-        <v>2.12051979</v>
+        <v>2.113973748</v>
       </c>
       <c r="P7">
-        <v>5.73325721</v>
+        <v>5.715558651999999</v>
       </c>
       <c r="Q7">
-        <v>9.433257210000001</v>
+        <v>9.415558651999998</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09683041222714253</v>
+        <v>0.09723213550119129</v>
       </c>
       <c r="T7">
-        <v>0.6113311891959504</v>
+        <v>0.616143730504823</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>65.7878455408627</v>
+        <v>54.82320461738558</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09360134737111982</v>
+        <v>0.0933778531264542</v>
       </c>
       <c r="C8">
-        <v>46.4130100741945</v>
+        <v>46.00082782455099</v>
       </c>
       <c r="D8">
-        <v>38.3050100741945</v>
+        <v>38.37482782455099</v>
       </c>
       <c r="E8">
-        <v>-19.908</v>
+        <v>-19.426</v>
       </c>
       <c r="F8">
-        <v>2.892</v>
+        <v>3.374</v>
       </c>
       <c r="G8">
         <v>11</v>
@@ -1943,28 +1943,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M8">
-        <v>0.1454676</v>
+        <v>0.1697122</v>
       </c>
       <c r="N8">
-        <v>7.829532399999999</v>
+        <v>7.805287799999999</v>
       </c>
       <c r="O8">
-        <v>2.113973748</v>
+        <v>2.107427706</v>
       </c>
       <c r="P8">
-        <v>5.715558651999999</v>
+        <v>5.697860093999999</v>
       </c>
       <c r="Q8">
-        <v>9.415558651999998</v>
+        <v>9.397860093999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09723213550119129</v>
+        <v>0.09764249798543463</v>
       </c>
       <c r="T8">
-        <v>0.616143730504823</v>
+        <v>0.621059767325714</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>54.82320461738559</v>
+        <v>46.99131824347336</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09337785312645419</v>
+        <v>0.09315435888178861</v>
       </c>
       <c r="C9">
-        <v>46.00082782455099</v>
+        <v>45.58890055038784</v>
       </c>
       <c r="D9">
-        <v>38.37482782455099</v>
+        <v>38.44490055038784</v>
       </c>
       <c r="E9">
-        <v>-19.426</v>
+        <v>-18.944</v>
       </c>
       <c r="F9">
-        <v>3.374000000000001</v>
+        <v>3.856</v>
       </c>
       <c r="G9">
         <v>11</v>
@@ -2025,28 +2025,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M9">
-        <v>0.1697122</v>
+        <v>0.1939568</v>
       </c>
       <c r="N9">
-        <v>7.805287799999999</v>
+        <v>7.781043199999999</v>
       </c>
       <c r="O9">
-        <v>2.107427706</v>
+        <v>2.100881664</v>
       </c>
       <c r="P9">
-        <v>5.697860093999999</v>
+        <v>5.680161535999999</v>
       </c>
       <c r="Q9">
-        <v>9.397860093999999</v>
+        <v>9.380161535999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09764249798543463</v>
+        <v>0.09806178139324848</v>
       </c>
       <c r="T9">
-        <v>0.621059767325714</v>
+        <v>0.6260826745122766</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>46.99131824347335</v>
+        <v>41.11740346303919</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09315435888178861</v>
+        <v>0.09293086463712301</v>
       </c>
       <c r="C10">
-        <v>45.58890055038784</v>
+        <v>45.17722965102168</v>
       </c>
       <c r="D10">
-        <v>38.44490055038784</v>
+        <v>38.51522965102168</v>
       </c>
       <c r="E10">
-        <v>-18.944</v>
+        <v>-18.462</v>
       </c>
       <c r="F10">
-        <v>3.856</v>
+        <v>4.338</v>
       </c>
       <c r="G10">
         <v>11</v>
@@ -2107,28 +2107,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M10">
-        <v>0.1939568</v>
+        <v>0.2182014</v>
       </c>
       <c r="N10">
-        <v>7.781043199999999</v>
+        <v>7.756798599999999</v>
       </c>
       <c r="O10">
-        <v>2.100881664</v>
+        <v>2.094335622</v>
       </c>
       <c r="P10">
-        <v>5.680161535999999</v>
+        <v>5.662462977999999</v>
       </c>
       <c r="Q10">
-        <v>9.380161535999999</v>
+        <v>9.362462978</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09806178139324848</v>
+        <v>0.09849027982101428</v>
       </c>
       <c r="T10">
-        <v>0.6260826745122766</v>
+        <v>0.6312159752633792</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>41.11740346303919</v>
+        <v>36.54880307825706</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09293086463712301</v>
+        <v>0.0927073703924574</v>
       </c>
       <c r="C11">
-        <v>45.17722965102168</v>
+        <v>44.76581653602728</v>
       </c>
       <c r="D11">
-        <v>38.51522965102168</v>
+        <v>38.58581653602728</v>
       </c>
       <c r="E11">
-        <v>-18.462</v>
+        <v>-17.98</v>
       </c>
       <c r="F11">
-        <v>4.338</v>
+        <v>4.82</v>
       </c>
       <c r="G11">
         <v>11</v>
@@ -2189,28 +2189,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M11">
-        <v>0.2182014</v>
+        <v>0.242446</v>
       </c>
       <c r="N11">
-        <v>7.756798599999999</v>
+        <v>7.732553999999999</v>
       </c>
       <c r="O11">
-        <v>2.094335622</v>
+        <v>2.08778958</v>
       </c>
       <c r="P11">
-        <v>5.662462977999999</v>
+        <v>5.644764419999999</v>
       </c>
       <c r="Q11">
-        <v>9.362462978</v>
+        <v>9.344764419999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09849027982101428</v>
+        <v>0.09892830043606377</v>
       </c>
       <c r="T11">
-        <v>0.6312159752633792</v>
+        <v>0.6364633493645062</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>36.54880307825706</v>
+        <v>32.89392277043135</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0927073703924574</v>
+        <v>0.09248387614779177</v>
       </c>
       <c r="C12">
-        <v>44.76581653602728</v>
+        <v>44.35466262533165</v>
       </c>
       <c r="D12">
-        <v>38.58581653602728</v>
+        <v>38.65666262533165</v>
       </c>
       <c r="E12">
-        <v>-17.98</v>
+        <v>-17.498</v>
       </c>
       <c r="F12">
-        <v>4.82</v>
+        <v>5.302</v>
       </c>
       <c r="G12">
         <v>11</v>
@@ -2271,28 +2271,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M12">
-        <v>0.242446</v>
+        <v>0.2666906</v>
       </c>
       <c r="N12">
-        <v>7.732553999999999</v>
+        <v>7.708309399999999</v>
       </c>
       <c r="O12">
-        <v>2.08778958</v>
+        <v>2.081243538</v>
       </c>
       <c r="P12">
-        <v>5.644764419999999</v>
+        <v>5.627065861999999</v>
       </c>
       <c r="Q12">
-        <v>9.344764419999999</v>
+        <v>9.327065862</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09892830043606377</v>
+        <v>0.099376164211002</v>
       </c>
       <c r="T12">
-        <v>0.6364633493645062</v>
+        <v>0.6418286419847596</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.89392277043135</v>
+        <v>29.90356615493759</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09248387614779177</v>
+        <v>0.09226038190312617</v>
       </c>
       <c r="C13">
-        <v>44.35466262533165</v>
+        <v>43.9437693493093</v>
       </c>
       <c r="D13">
-        <v>38.65666262533165</v>
+        <v>38.7277693493093</v>
       </c>
       <c r="E13">
-        <v>-17.498</v>
+        <v>-17.016</v>
       </c>
       <c r="F13">
-        <v>5.302</v>
+        <v>5.784</v>
       </c>
       <c r="G13">
         <v>11</v>
@@ -2353,28 +2353,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M13">
-        <v>0.2666906</v>
+        <v>0.2909351999999999</v>
       </c>
       <c r="N13">
-        <v>7.708309399999999</v>
+        <v>7.684064799999999</v>
       </c>
       <c r="O13">
-        <v>2.081243538</v>
+        <v>2.074697496</v>
       </c>
       <c r="P13">
-        <v>5.627065861999999</v>
+        <v>5.609367303999999</v>
       </c>
       <c r="Q13">
-        <v>9.327065862</v>
+        <v>9.309367303999998</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.099376164211002</v>
+        <v>0.09983420670809792</v>
       </c>
       <c r="T13">
-        <v>0.6418286419847596</v>
+        <v>0.6473158730736553</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.90356615493759</v>
+        <v>27.4116023086928</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09226038190312617</v>
+        <v>0.09203688765846056</v>
       </c>
       <c r="C14">
-        <v>43.9437693493093</v>
+        <v>43.53313814887855</v>
       </c>
       <c r="D14">
-        <v>38.7277693493093</v>
+        <v>38.79913814887855</v>
       </c>
       <c r="E14">
-        <v>-17.016</v>
+        <v>-16.534</v>
       </c>
       <c r="F14">
-        <v>5.784</v>
+        <v>6.266000000000001</v>
       </c>
       <c r="G14">
         <v>11</v>
@@ -2435,28 +2435,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M14">
-        <v>0.2909351999999999</v>
+        <v>0.3151798</v>
       </c>
       <c r="N14">
-        <v>7.684064799999999</v>
+        <v>7.659820199999999</v>
       </c>
       <c r="O14">
-        <v>2.074697496</v>
+        <v>2.068151454</v>
       </c>
       <c r="P14">
-        <v>5.609367303999999</v>
+        <v>5.591668745999999</v>
       </c>
       <c r="Q14">
-        <v>9.309367303999998</v>
+        <v>9.291668745999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09983420670809792</v>
+        <v>0.1003027789177708</v>
       </c>
       <c r="T14">
-        <v>0.6473158730736553</v>
+        <v>0.6529292474059737</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.4116023086928</v>
+        <v>25.30301751571642</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09203688765846056</v>
+        <v>0.09181339341379498</v>
       </c>
       <c r="C15">
-        <v>43.53313814887855</v>
+        <v>43.12277047559876</v>
       </c>
       <c r="D15">
-        <v>38.79913814887855</v>
+        <v>38.87077047559876</v>
       </c>
       <c r="E15">
-        <v>-16.534</v>
+        <v>-16.052</v>
       </c>
       <c r="F15">
-        <v>6.266000000000001</v>
+        <v>6.748000000000001</v>
       </c>
       <c r="G15">
         <v>11</v>
@@ -2517,28 +2517,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M15">
-        <v>0.3151798</v>
+        <v>0.3394244</v>
       </c>
       <c r="N15">
-        <v>7.659820199999999</v>
+        <v>7.635575599999998</v>
       </c>
       <c r="O15">
-        <v>2.068151454</v>
+        <v>2.061605412</v>
       </c>
       <c r="P15">
-        <v>5.591668745999999</v>
+        <v>5.573970187999999</v>
       </c>
       <c r="Q15">
-        <v>9.291668745999999</v>
+        <v>9.273970188</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1003027789177708</v>
+        <v>0.1007822481555755</v>
       </c>
       <c r="T15">
-        <v>0.6529292474059737</v>
+        <v>0.6586731653274159</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.30301751571642</v>
+        <v>23.49565912173668</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09181339341379498</v>
+        <v>0.09158989916912935</v>
       </c>
       <c r="C16">
-        <v>43.12277047559876</v>
+        <v>42.71266779176885</v>
       </c>
       <c r="D16">
-        <v>38.87077047559876</v>
+        <v>38.94266779176886</v>
       </c>
       <c r="E16">
-        <v>-16.052</v>
+        <v>-15.57</v>
       </c>
       <c r="F16">
-        <v>6.748000000000001</v>
+        <v>7.230000000000001</v>
       </c>
       <c r="G16">
         <v>11</v>
@@ -2599,28 +2599,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M16">
-        <v>0.3394244</v>
+        <v>0.3636690000000001</v>
       </c>
       <c r="N16">
-        <v>7.635575599999998</v>
+        <v>7.611330999999999</v>
       </c>
       <c r="O16">
-        <v>2.061605412</v>
+        <v>2.05505937</v>
       </c>
       <c r="P16">
-        <v>5.573970187999999</v>
+        <v>5.556271629999999</v>
       </c>
       <c r="Q16">
-        <v>9.273970188</v>
+        <v>9.256271630000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1007822481555755</v>
+        <v>0.1012729990225051</v>
       </c>
       <c r="T16">
-        <v>0.6586731653274159</v>
+        <v>0.6645522342587744</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.49565912173668</v>
+        <v>21.92928184695423</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09158989916912935</v>
+        <v>0.09136640492446375</v>
       </c>
       <c r="C17">
-        <v>42.71266779176885</v>
+        <v>42.30283157052673</v>
       </c>
       <c r="D17">
-        <v>38.94266779176886</v>
+        <v>39.01483157052674</v>
       </c>
       <c r="E17">
-        <v>-15.57</v>
+        <v>-15.088</v>
       </c>
       <c r="F17">
-        <v>7.23</v>
+        <v>7.712000000000001</v>
       </c>
       <c r="G17">
         <v>11</v>
@@ -2681,28 +2681,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M17">
-        <v>0.363669</v>
+        <v>0.3879136</v>
       </c>
       <c r="N17">
-        <v>7.611330999999999</v>
+        <v>7.587086399999999</v>
       </c>
       <c r="O17">
-        <v>2.05505937</v>
+        <v>2.048513328</v>
       </c>
       <c r="P17">
-        <v>5.556271629999999</v>
+        <v>5.538573071999998</v>
       </c>
       <c r="Q17">
-        <v>9.256271630000001</v>
+        <v>9.238573071999998</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1012729990225051</v>
+        <v>0.1017754344338854</v>
       </c>
       <c r="T17">
-        <v>0.6645522342587744</v>
+        <v>0.6705712810218318</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.92928184695423</v>
+        <v>20.55870173151959</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09136640492446375</v>
+        <v>0.09114291067979814</v>
       </c>
       <c r="C18">
-        <v>42.30283157052673</v>
+        <v>41.89326329594991</v>
       </c>
       <c r="D18">
-        <v>39.01483157052674</v>
+        <v>39.08726329594991</v>
       </c>
       <c r="E18">
-        <v>-15.088</v>
+        <v>-14.606</v>
       </c>
       <c r="F18">
-        <v>7.712000000000001</v>
+        <v>8.194000000000001</v>
       </c>
       <c r="G18">
         <v>11</v>
@@ -2763,28 +2763,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M18">
-        <v>0.3879136</v>
+        <v>0.4121582</v>
       </c>
       <c r="N18">
-        <v>7.587086399999999</v>
+        <v>7.562841799999998</v>
       </c>
       <c r="O18">
-        <v>2.048513328</v>
+        <v>2.041967286</v>
       </c>
       <c r="P18">
-        <v>5.538573071999998</v>
+        <v>5.520874513999999</v>
       </c>
       <c r="Q18">
-        <v>9.238573071999998</v>
+        <v>9.220874513999998</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1017754344338854</v>
+        <v>0.1022899767226484</v>
       </c>
       <c r="T18">
-        <v>0.6705712810218318</v>
+        <v>0.6767353650562883</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.55870173151959</v>
+        <v>19.34936633554785</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09114291067979814</v>
+        <v>0.09091941643513253</v>
       </c>
       <c r="C19">
-        <v>41.89326329594991</v>
+        <v>41.48396446315731</v>
       </c>
       <c r="D19">
-        <v>39.08726329594991</v>
+        <v>39.15996446315731</v>
       </c>
       <c r="E19">
-        <v>-14.606</v>
+        <v>-14.124</v>
       </c>
       <c r="F19">
-        <v>8.194000000000001</v>
+        <v>8.676000000000002</v>
       </c>
       <c r="G19">
         <v>11</v>
@@ -2845,28 +2845,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M19">
-        <v>0.4121582</v>
+        <v>0.4364028000000001</v>
       </c>
       <c r="N19">
-        <v>7.562841799999998</v>
+        <v>7.538597199999999</v>
       </c>
       <c r="O19">
-        <v>2.041967286</v>
+        <v>2.035421244</v>
       </c>
       <c r="P19">
-        <v>5.520874513999999</v>
+        <v>5.503175956</v>
       </c>
       <c r="Q19">
-        <v>9.220874513999998</v>
+        <v>9.203175955999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1022899767226484</v>
+        <v>0.1028170688233324</v>
       </c>
       <c r="T19">
-        <v>0.6767353650562883</v>
+        <v>0.6830497926037802</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.34936633554785</v>
+        <v>18.27440153912852</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09091941643513254</v>
+        <v>0.09069592219046693</v>
       </c>
       <c r="C20">
-        <v>41.48396446315731</v>
+        <v>41.07493657841204</v>
       </c>
       <c r="D20">
-        <v>39.15996446315731</v>
+        <v>39.23293657841204</v>
       </c>
       <c r="E20">
-        <v>-14.124</v>
+        <v>-13.642</v>
       </c>
       <c r="F20">
-        <v>8.676</v>
+        <v>9.158000000000001</v>
       </c>
       <c r="G20">
         <v>11</v>
@@ -2927,28 +2927,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M20">
-        <v>0.4364028</v>
+        <v>0.4606474</v>
       </c>
       <c r="N20">
-        <v>7.538597199999999</v>
+        <v>7.514352599999999</v>
       </c>
       <c r="O20">
-        <v>2.035421244</v>
+        <v>2.028875202</v>
       </c>
       <c r="P20">
-        <v>5.503175956</v>
+        <v>5.485477397999999</v>
       </c>
       <c r="Q20">
-        <v>9.203175955999999</v>
+        <v>9.185477398</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1028170688233324</v>
+        <v>0.1033571755437863</v>
       </c>
       <c r="T20">
-        <v>0.6830497926037802</v>
+        <v>0.6895201319425683</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.27440153912853</v>
+        <v>17.31259093180597</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09069592219046693</v>
+        <v>0.09047242794580133</v>
       </c>
       <c r="C21">
-        <v>41.07493657841204</v>
+        <v>40.6661811592255</v>
       </c>
       <c r="D21">
-        <v>39.23293657841204</v>
+        <v>39.3061811592255</v>
       </c>
       <c r="E21">
-        <v>-13.642</v>
+        <v>-13.16</v>
       </c>
       <c r="F21">
-        <v>9.158000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G21">
         <v>11</v>
@@ -3009,28 +3009,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M21">
-        <v>0.4606474</v>
+        <v>0.484892</v>
       </c>
       <c r="N21">
-        <v>7.514352599999999</v>
+        <v>7.490107999999998</v>
       </c>
       <c r="O21">
-        <v>2.028875202</v>
+        <v>2.02232916</v>
       </c>
       <c r="P21">
-        <v>5.485477397999999</v>
+        <v>5.467778839999999</v>
       </c>
       <c r="Q21">
-        <v>9.185477398</v>
+        <v>9.16777884</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1033571755437863</v>
+        <v>0.1039107849322517</v>
       </c>
       <c r="T21">
-        <v>0.6895201319425683</v>
+        <v>0.696152229764826</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.31259093180597</v>
+        <v>16.44696138521567</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09047242794580133</v>
+        <v>0.09024893370113571</v>
       </c>
       <c r="C22">
-        <v>40.6661811592255</v>
+        <v>40.25769973446258</v>
       </c>
       <c r="D22">
-        <v>39.3061811592255</v>
+        <v>39.37969973446258</v>
       </c>
       <c r="E22">
-        <v>-13.16</v>
+        <v>-12.678</v>
       </c>
       <c r="F22">
-        <v>9.640000000000001</v>
+        <v>10.122</v>
       </c>
       <c r="G22">
         <v>11</v>
@@ -3091,28 +3091,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M22">
-        <v>0.484892</v>
+        <v>0.5091366000000001</v>
       </c>
       <c r="N22">
-        <v>7.490107999999998</v>
+        <v>7.465863399999999</v>
       </c>
       <c r="O22">
-        <v>2.02232916</v>
+        <v>2.015783118</v>
       </c>
       <c r="P22">
-        <v>5.467778839999999</v>
+        <v>5.450080281999999</v>
       </c>
       <c r="Q22">
-        <v>9.16777884</v>
+        <v>9.150080281999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1039107849322517</v>
+        <v>0.104478409748273</v>
       </c>
       <c r="T22">
-        <v>0.696152229764826</v>
+        <v>0.7029522287977739</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.44696138521567</v>
+        <v>15.66377274782445</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09024893370113571</v>
+        <v>0.09002543945647012</v>
       </c>
       <c r="C23">
-        <v>40.25769973446258</v>
+        <v>39.84949384444792</v>
       </c>
       <c r="D23">
-        <v>39.37969973446258</v>
+        <v>39.45349384444792</v>
       </c>
       <c r="E23">
-        <v>-12.678</v>
+        <v>-12.196</v>
       </c>
       <c r="F23">
-        <v>10.122</v>
+        <v>10.604</v>
       </c>
       <c r="G23">
         <v>11</v>
@@ -3173,28 +3173,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M23">
-        <v>0.5091365999999999</v>
+        <v>0.5333812</v>
       </c>
       <c r="N23">
-        <v>7.465863399999999</v>
+        <v>7.441618799999999</v>
       </c>
       <c r="O23">
-        <v>2.015783118</v>
+        <v>2.009237076</v>
       </c>
       <c r="P23">
-        <v>5.450080281999999</v>
+        <v>5.432381723999999</v>
       </c>
       <c r="Q23">
-        <v>9.150080281999999</v>
+        <v>9.132381723999998</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.104478409748273</v>
+        <v>0.1050605890467566</v>
       </c>
       <c r="T23">
-        <v>0.7029522287977739</v>
+        <v>0.7099265867802844</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.66377274782445</v>
+        <v>14.95178307746879</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09002543945647012</v>
+        <v>0.0898019452118045</v>
       </c>
       <c r="C24">
-        <v>39.84949384444792</v>
+        <v>39.44156504107367</v>
       </c>
       <c r="D24">
-        <v>39.45349384444792</v>
+        <v>39.52756504107367</v>
       </c>
       <c r="E24">
-        <v>-12.196</v>
+        <v>-11.714</v>
       </c>
       <c r="F24">
-        <v>10.604</v>
+        <v>11.086</v>
       </c>
       <c r="G24">
         <v>11</v>
@@ -3255,28 +3255,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M24">
-        <v>0.5333812</v>
+        <v>0.5576257999999999</v>
       </c>
       <c r="N24">
-        <v>7.441618799999999</v>
+        <v>7.417374199999998</v>
       </c>
       <c r="O24">
-        <v>2.009237076</v>
+        <v>2.002691034</v>
       </c>
       <c r="P24">
-        <v>5.432381723999999</v>
+        <v>5.414683165999999</v>
       </c>
       <c r="Q24">
-        <v>9.132381723999998</v>
+        <v>9.114683165999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1050605890467566</v>
+        <v>0.1056578898854604</v>
       </c>
       <c r="T24">
-        <v>0.7099265867802844</v>
+        <v>0.7170820969181849</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.95178307746879</v>
+        <v>14.30170555236146</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0898019452118045</v>
+        <v>0.08957845096713889</v>
       </c>
       <c r="C25">
-        <v>39.44156504107367</v>
+        <v>39.03391488790811</v>
       </c>
       <c r="D25">
-        <v>39.52756504107367</v>
+        <v>39.60191488790812</v>
       </c>
       <c r="E25">
-        <v>-11.714</v>
+        <v>-11.232</v>
       </c>
       <c r="F25">
-        <v>11.086</v>
+        <v>11.568</v>
       </c>
       <c r="G25">
         <v>11</v>
@@ -3337,28 +3337,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M25">
-        <v>0.5576257999999999</v>
+        <v>0.5818704</v>
       </c>
       <c r="N25">
-        <v>7.417374199999998</v>
+        <v>7.393129599999999</v>
       </c>
       <c r="O25">
-        <v>2.002691034</v>
+        <v>1.996144992</v>
       </c>
       <c r="P25">
-        <v>5.414683165999999</v>
+        <v>5.396984607999999</v>
       </c>
       <c r="Q25">
-        <v>9.114683165999999</v>
+        <v>9.096984608</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1056578898854604</v>
+        <v>0.106270909167288</v>
       </c>
       <c r="T25">
-        <v>0.7170820969181849</v>
+        <v>0.7244259099544512</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.30170555236146</v>
+        <v>13.7058011543464</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08957845096713889</v>
+        <v>0.08935495672247329</v>
       </c>
       <c r="C26">
-        <v>39.03391488790812</v>
+        <v>38.62654496030578</v>
       </c>
       <c r="D26">
-        <v>39.60191488790812</v>
+        <v>39.67654496030578</v>
       </c>
       <c r="E26">
-        <v>-11.232</v>
+        <v>-10.75</v>
       </c>
       <c r="F26">
-        <v>11.568</v>
+        <v>12.05</v>
       </c>
       <c r="G26">
         <v>11</v>
@@ -3419,28 +3419,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M26">
-        <v>0.5818703999999999</v>
+        <v>0.606115</v>
       </c>
       <c r="N26">
-        <v>7.393129599999999</v>
+        <v>7.368884999999999</v>
       </c>
       <c r="O26">
-        <v>1.996144992</v>
+        <v>1.98959895</v>
       </c>
       <c r="P26">
-        <v>5.396984607999999</v>
+        <v>5.379286049999999</v>
       </c>
       <c r="Q26">
-        <v>9.096984608</v>
+        <v>9.07928605</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.106270909167288</v>
+        <v>0.1069002756299644</v>
       </c>
       <c r="T26">
-        <v>0.7244259099544512</v>
+        <v>0.7319655580050179</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.7058011543464</v>
+        <v>13.15756910817254</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08935495672247329</v>
+        <v>0.08941616247780769</v>
       </c>
       <c r="C27">
-        <v>38.62654496030578</v>
+        <v>38.12407894166491</v>
       </c>
       <c r="D27">
-        <v>39.67654496030578</v>
+        <v>39.65607894166492</v>
       </c>
       <c r="E27">
-        <v>-10.75</v>
+        <v>-10.268</v>
       </c>
       <c r="F27">
-        <v>12.05</v>
+        <v>12.532</v>
       </c>
       <c r="G27">
         <v>11</v>
@@ -3501,45 +3501,45 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M27">
-        <v>0.606115</v>
+        <v>0.6491576000000001</v>
       </c>
       <c r="N27">
-        <v>7.368884999999999</v>
+        <v>7.325842399999999</v>
       </c>
       <c r="O27">
-        <v>1.98959895</v>
+        <v>1.977977448</v>
       </c>
       <c r="P27">
-        <v>5.379286049999999</v>
+        <v>5.347864951999999</v>
       </c>
       <c r="Q27">
-        <v>9.07928605</v>
+        <v>9.047864951999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1069002756299644</v>
+        <v>0.1075466519970374</v>
       </c>
       <c r="T27">
-        <v>0.7319655580050179</v>
+        <v>0.7397089803272215</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.27</v>
       </c>
       <c r="W27">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>13.15756910817254</v>
+        <v>12.2851523266461</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08941616247780769</v>
+        <v>0.08920361823314207</v>
       </c>
       <c r="C28">
-        <v>38.12407894166491</v>
+        <v>37.71324042709262</v>
       </c>
       <c r="D28">
-        <v>39.65607894166492</v>
+        <v>39.72724042709262</v>
       </c>
       <c r="E28">
-        <v>-10.268</v>
+        <v>-9.786</v>
       </c>
       <c r="F28">
-        <v>12.532</v>
+        <v>13.014</v>
       </c>
       <c r="G28">
         <v>11</v>
@@ -3583,28 +3583,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M28">
-        <v>0.6491576000000001</v>
+        <v>0.6741252000000001</v>
       </c>
       <c r="N28">
-        <v>7.325842399999999</v>
+        <v>7.300874799999999</v>
       </c>
       <c r="O28">
-        <v>1.977977448</v>
+        <v>1.971236196</v>
       </c>
       <c r="P28">
-        <v>5.347864951999999</v>
+        <v>5.329638603999999</v>
       </c>
       <c r="Q28">
-        <v>9.047864951999999</v>
+        <v>9.029638603999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1075466519970374</v>
+        <v>0.1082107373056741</v>
       </c>
       <c r="T28">
-        <v>0.7397089803272215</v>
+        <v>0.7476645512061979</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.2851523266461</v>
+        <v>11.83014668491847</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08920361823314207</v>
+        <v>0.08899107398847647</v>
       </c>
       <c r="C29">
-        <v>37.71324042709262</v>
+        <v>37.30265776537205</v>
       </c>
       <c r="D29">
-        <v>39.72724042709262</v>
+        <v>39.79865776537205</v>
       </c>
       <c r="E29">
-        <v>-9.786</v>
+        <v>-9.303999999999998</v>
       </c>
       <c r="F29">
-        <v>13.014</v>
+        <v>13.496</v>
       </c>
       <c r="G29">
         <v>11</v>
@@ -3665,28 +3665,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M29">
-        <v>0.6741252000000001</v>
+        <v>0.6990928000000001</v>
       </c>
       <c r="N29">
-        <v>7.300874799999999</v>
+        <v>7.275907199999999</v>
       </c>
       <c r="O29">
-        <v>1.971236196</v>
+        <v>1.964494944</v>
       </c>
       <c r="P29">
-        <v>5.329638603999999</v>
+        <v>5.311412255999999</v>
       </c>
       <c r="Q29">
-        <v>9.029638603999999</v>
+        <v>9.011412256</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1082107373056741</v>
+        <v>0.1088932694284395</v>
       </c>
       <c r="T29">
-        <v>0.7476645512061979</v>
+        <v>0.7558411101651459</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.83014668491847</v>
+        <v>11.40764144617138</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08899107398847647</v>
+        <v>0.08877852974381086</v>
       </c>
       <c r="C30">
-        <v>37.30265776537205</v>
+        <v>36.89233233882198</v>
       </c>
       <c r="D30">
-        <v>39.79865776537205</v>
+        <v>39.87033233882198</v>
       </c>
       <c r="E30">
-        <v>-9.303999999999998</v>
+        <v>-8.821999999999997</v>
       </c>
       <c r="F30">
-        <v>13.496</v>
+        <v>13.978</v>
       </c>
       <c r="G30">
         <v>11</v>
@@ -3747,28 +3747,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M30">
-        <v>0.6990928000000001</v>
+        <v>0.7240604000000002</v>
       </c>
       <c r="N30">
-        <v>7.275907199999999</v>
+        <v>7.250939599999999</v>
       </c>
       <c r="O30">
-        <v>1.964494944</v>
+        <v>1.957753692</v>
       </c>
       <c r="P30">
-        <v>5.311412255999999</v>
+        <v>5.293185907999999</v>
       </c>
       <c r="Q30">
-        <v>9.011412256</v>
+        <v>8.993185907999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1088932694284395</v>
+        <v>0.1095950278081843</v>
       </c>
       <c r="T30">
-        <v>0.7558411101651459</v>
+        <v>0.7642479947285712</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.40764144617138</v>
+        <v>11.01427449975168</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08877852974381086</v>
+        <v>0.08856598549914525</v>
       </c>
       <c r="C31">
-        <v>36.89233233882198</v>
+        <v>36.482265539737</v>
       </c>
       <c r="D31">
-        <v>39.87033233882198</v>
+        <v>39.942265539737</v>
       </c>
       <c r="E31">
-        <v>-8.822000000000001</v>
+        <v>-8.34</v>
       </c>
       <c r="F31">
-        <v>13.978</v>
+        <v>14.46</v>
       </c>
       <c r="G31">
         <v>11</v>
@@ -3829,28 +3829,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M31">
-        <v>0.7240603999999999</v>
+        <v>0.749028</v>
       </c>
       <c r="N31">
-        <v>7.250939599999999</v>
+        <v>7.225971999999999</v>
       </c>
       <c r="O31">
-        <v>1.957753692</v>
+        <v>1.95101244</v>
       </c>
       <c r="P31">
-        <v>5.293185907999999</v>
+        <v>5.274959559999999</v>
       </c>
       <c r="Q31">
-        <v>8.993185907999999</v>
+        <v>8.974959559999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1095950278081843</v>
+        <v>0.1103168364273504</v>
       </c>
       <c r="T31">
-        <v>0.7642479947285712</v>
+        <v>0.7728950759938087</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.01427449975168</v>
+        <v>10.64713201642662</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08856598549914525</v>
+        <v>0.08835344125447965</v>
       </c>
       <c r="C32">
-        <v>36.482265539737</v>
+        <v>36.07245877047763</v>
       </c>
       <c r="D32">
-        <v>39.942265539737</v>
+        <v>40.01445877047763</v>
       </c>
       <c r="E32">
-        <v>-8.34</v>
+        <v>-7.858000000000001</v>
       </c>
       <c r="F32">
-        <v>14.46</v>
+        <v>14.942</v>
       </c>
       <c r="G32">
         <v>11</v>
@@ -3911,28 +3911,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M32">
-        <v>0.749028</v>
+        <v>0.7739956</v>
       </c>
       <c r="N32">
-        <v>7.225971999999999</v>
+        <v>7.201004399999999</v>
       </c>
       <c r="O32">
-        <v>1.95101244</v>
+        <v>1.944271188</v>
       </c>
       <c r="P32">
-        <v>5.274959559999999</v>
+        <v>5.256733211999999</v>
       </c>
       <c r="Q32">
-        <v>8.974959559999999</v>
+        <v>8.956733212</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1103168364273504</v>
+        <v>0.1110595670354778</v>
       </c>
       <c r="T32">
-        <v>0.7728950759938087</v>
+        <v>0.7817927972957197</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.64713201642662</v>
+        <v>10.30367614492899</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08835344125447965</v>
+        <v>0.08814089700981403</v>
       </c>
       <c r="C33">
-        <v>36.07245877047763</v>
+        <v>35.66291344356152</v>
       </c>
       <c r="D33">
-        <v>40.01445877047763</v>
+        <v>40.08691344356152</v>
       </c>
       <c r="E33">
-        <v>-7.858000000000001</v>
+        <v>-7.375999999999999</v>
       </c>
       <c r="F33">
-        <v>14.942</v>
+        <v>15.424</v>
       </c>
       <c r="G33">
         <v>11</v>
@@ -3993,28 +3993,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M33">
-        <v>0.7739956</v>
+        <v>0.7989632000000001</v>
       </c>
       <c r="N33">
-        <v>7.201004399999999</v>
+        <v>7.176036799999999</v>
       </c>
       <c r="O33">
-        <v>1.944271188</v>
+        <v>1.937529936</v>
       </c>
       <c r="P33">
-        <v>5.256733211999999</v>
+        <v>5.238506863999999</v>
       </c>
       <c r="Q33">
-        <v>8.956733212</v>
+        <v>8.938506863999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1110595670354778</v>
+        <v>0.1118241426614912</v>
       </c>
       <c r="T33">
-        <v>0.7817927972957197</v>
+        <v>0.7909522162829811</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.30367614492899</v>
+        <v>9.981686265399956</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08814089700981403</v>
+        <v>0.08833788276514844</v>
       </c>
       <c r="C34">
-        <v>35.66291344356152</v>
+        <v>35.11375365229154</v>
       </c>
       <c r="D34">
-        <v>40.08691344356152</v>
+        <v>40.01975365229154</v>
       </c>
       <c r="E34">
-        <v>-7.375999999999999</v>
+        <v>-6.893999999999998</v>
       </c>
       <c r="F34">
-        <v>15.424</v>
+        <v>15.906</v>
       </c>
       <c r="G34">
         <v>11</v>
@@ -4075,45 +4075,45 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M34">
-        <v>0.7989632000000001</v>
+        <v>0.8509710000000001</v>
       </c>
       <c r="N34">
-        <v>7.176036799999999</v>
+        <v>7.124028999999998</v>
       </c>
       <c r="O34">
-        <v>1.937529936</v>
+        <v>1.92348783</v>
       </c>
       <c r="P34">
-        <v>5.238506863999999</v>
+        <v>5.200541169999998</v>
       </c>
       <c r="Q34">
-        <v>8.938506863999999</v>
+        <v>8.900541169999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1118241426614912</v>
+        <v>0.1126115414405201</v>
       </c>
       <c r="T34">
-        <v>0.7909522162829811</v>
+        <v>0.8003850507623995</v>
       </c>
       <c r="U34">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.27</v>
       </c>
       <c r="W34">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>9.981686265399956</v>
+        <v>9.371647212419692</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08833788276514844</v>
+        <v>0.08813774852048284</v>
       </c>
       <c r="C35">
-        <v>35.11375365229154</v>
+        <v>34.69998871125634</v>
       </c>
       <c r="D35">
-        <v>40.01975365229154</v>
+        <v>40.08798871125634</v>
       </c>
       <c r="E35">
-        <v>-6.893999999999998</v>
+        <v>-6.411999999999999</v>
       </c>
       <c r="F35">
-        <v>15.906</v>
+        <v>16.388</v>
       </c>
       <c r="G35">
         <v>11</v>
@@ -4157,28 +4157,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M35">
-        <v>0.8509710000000001</v>
+        <v>0.876758</v>
       </c>
       <c r="N35">
-        <v>7.124028999999998</v>
+        <v>7.098241999999999</v>
       </c>
       <c r="O35">
-        <v>1.92348783</v>
+        <v>1.91652534</v>
       </c>
       <c r="P35">
-        <v>5.200541169999998</v>
+        <v>5.181716659999999</v>
       </c>
       <c r="Q35">
-        <v>8.900541169999999</v>
+        <v>8.881716659999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1126115414405201</v>
+        <v>0.1134228007886104</v>
       </c>
       <c r="T35">
-        <v>0.8003850507623995</v>
+        <v>0.8101037287108911</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.371647212419692</v>
+        <v>9.096010529701466</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08813774852048284</v>
+        <v>0.08793761427581723</v>
       </c>
       <c r="C36">
-        <v>34.69998871125634</v>
+        <v>34.28645685389034</v>
       </c>
       <c r="D36">
-        <v>40.08798871125634</v>
+        <v>40.15645685389035</v>
       </c>
       <c r="E36">
-        <v>-6.411999999999999</v>
+        <v>-5.93</v>
       </c>
       <c r="F36">
-        <v>16.388</v>
+        <v>16.87</v>
       </c>
       <c r="G36">
         <v>11</v>
@@ -4239,28 +4239,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M36">
-        <v>0.876758</v>
+        <v>0.902545</v>
       </c>
       <c r="N36">
-        <v>7.098241999999999</v>
+        <v>7.072454999999999</v>
       </c>
       <c r="O36">
-        <v>1.91652534</v>
+        <v>1.90956285</v>
       </c>
       <c r="P36">
-        <v>5.181716659999999</v>
+        <v>5.162892149999999</v>
       </c>
       <c r="Q36">
-        <v>8.881716659999999</v>
+        <v>8.86289215</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1134228007886104</v>
+        <v>0.1142590219627957</v>
       </c>
       <c r="T36">
-        <v>0.8101037287108911</v>
+        <v>0.8201214429039518</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.096010529701466</v>
+        <v>8.836124514567139</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08793761427581723</v>
+        <v>0.0877374800311516</v>
       </c>
       <c r="C37">
-        <v>34.28645685389034</v>
+        <v>33.87315927652017</v>
       </c>
       <c r="D37">
-        <v>40.15645685389035</v>
+        <v>40.22515927652017</v>
       </c>
       <c r="E37">
-        <v>-5.93</v>
+        <v>-5.447999999999997</v>
       </c>
       <c r="F37">
-        <v>16.87</v>
+        <v>17.352</v>
       </c>
       <c r="G37">
         <v>11</v>
@@ -4321,28 +4321,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M37">
-        <v>0.902545</v>
+        <v>0.9283320000000002</v>
       </c>
       <c r="N37">
-        <v>7.072454999999999</v>
+        <v>7.046667999999999</v>
       </c>
       <c r="O37">
-        <v>1.90956285</v>
+        <v>1.90260036</v>
       </c>
       <c r="P37">
-        <v>5.162892149999999</v>
+        <v>5.144067639999999</v>
       </c>
       <c r="Q37">
-        <v>8.86289215</v>
+        <v>8.844067639999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1142590219627957</v>
+        <v>0.1151213750486744</v>
       </c>
       <c r="T37">
-        <v>0.8201214429039518</v>
+        <v>0.8304522106655456</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.836124514567139</v>
+        <v>8.590676611384717</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08773748003115162</v>
+        <v>0.08753734578648602</v>
       </c>
       <c r="C38">
-        <v>33.87315927652017</v>
+        <v>33.46009718367348</v>
       </c>
       <c r="D38">
-        <v>40.22515927652017</v>
+        <v>40.29409718367349</v>
       </c>
       <c r="E38">
-        <v>-5.448</v>
+        <v>-4.966000000000001</v>
       </c>
       <c r="F38">
-        <v>17.352</v>
+        <v>17.834</v>
       </c>
       <c r="G38">
         <v>11</v>
@@ -4403,28 +4403,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M38">
-        <v>0.928332</v>
+        <v>0.9541189999999999</v>
       </c>
       <c r="N38">
-        <v>7.046667999999999</v>
+        <v>7.020880999999999</v>
       </c>
       <c r="O38">
-        <v>1.90260036</v>
+        <v>1.89563787</v>
       </c>
       <c r="P38">
-        <v>5.144067639999999</v>
+        <v>5.125243129999999</v>
       </c>
       <c r="Q38">
-        <v>8.844067639999999</v>
+        <v>8.82524313</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1151213750486744</v>
+        <v>0.1160111044229937</v>
       </c>
       <c r="T38">
-        <v>0.8304522106655456</v>
+        <v>0.8411109393084598</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.590676611384719</v>
+        <v>8.358496162428377</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08753734578648602</v>
+        <v>0.08733721154182042</v>
       </c>
       <c r="C39">
-        <v>33.46009718367348</v>
+        <v>33.04727178814944</v>
       </c>
       <c r="D39">
-        <v>40.29409718367349</v>
+        <v>40.36327178814944</v>
       </c>
       <c r="E39">
-        <v>-4.966000000000001</v>
+        <v>-4.483999999999998</v>
       </c>
       <c r="F39">
-        <v>17.834</v>
+        <v>18.316</v>
       </c>
       <c r="G39">
         <v>11</v>
@@ -4485,28 +4485,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M39">
-        <v>0.9541189999999999</v>
+        <v>0.9799060000000002</v>
       </c>
       <c r="N39">
-        <v>7.020880999999999</v>
+        <v>6.995093999999998</v>
       </c>
       <c r="O39">
-        <v>1.89563787</v>
+        <v>1.88867538</v>
       </c>
       <c r="P39">
-        <v>5.125243129999999</v>
+        <v>5.106418619999999</v>
       </c>
       <c r="Q39">
-        <v>8.82524313</v>
+        <v>8.806418619999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1160111044229937</v>
+        <v>0.1169295347448716</v>
       </c>
       <c r="T39">
-        <v>0.8411109393084598</v>
+        <v>0.8521134979075972</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.358496162428377</v>
+        <v>8.138535737101311</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08733721154182042</v>
+        <v>0.08713707729715481</v>
       </c>
       <c r="C40">
-        <v>33.04727178814944</v>
+        <v>32.63468431108976</v>
       </c>
       <c r="D40">
-        <v>40.36327178814944</v>
+        <v>40.43268431108976</v>
       </c>
       <c r="E40">
-        <v>-4.483999999999998</v>
+        <v>-4.001999999999999</v>
       </c>
       <c r="F40">
-        <v>18.316</v>
+        <v>18.798</v>
       </c>
       <c r="G40">
         <v>11</v>
@@ -4567,28 +4567,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M40">
-        <v>0.9799060000000002</v>
+        <v>1.005693</v>
       </c>
       <c r="N40">
-        <v>6.995093999999998</v>
+        <v>6.969306999999999</v>
       </c>
       <c r="O40">
-        <v>1.88867538</v>
+        <v>1.88171289</v>
       </c>
       <c r="P40">
-        <v>5.106418619999999</v>
+        <v>5.08759411</v>
       </c>
       <c r="Q40">
-        <v>8.806418619999999</v>
+        <v>8.787594110000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1169295347448716</v>
+        <v>0.1178780775363193</v>
       </c>
       <c r="T40">
-        <v>0.8521134979075972</v>
+        <v>0.8634767961329357</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.138535737101311</v>
+        <v>7.929855333585893</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08713707729715481</v>
+        <v>0.0869369430524892</v>
       </c>
       <c r="C41">
-        <v>32.63468431108976</v>
+        <v>32.22233598205058</v>
       </c>
       <c r="D41">
-        <v>40.43268431108976</v>
+        <v>40.50233598205058</v>
       </c>
       <c r="E41">
-        <v>-4.001999999999999</v>
+        <v>-3.52</v>
       </c>
       <c r="F41">
-        <v>18.798</v>
+        <v>19.28</v>
       </c>
       <c r="G41">
         <v>11</v>
@@ -4649,28 +4649,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M41">
-        <v>1.005693</v>
+        <v>1.03148</v>
       </c>
       <c r="N41">
-        <v>6.969306999999999</v>
+        <v>6.943519999999999</v>
       </c>
       <c r="O41">
-        <v>1.88171289</v>
+        <v>1.8747504</v>
       </c>
       <c r="P41">
-        <v>5.08759411</v>
+        <v>5.068769599999999</v>
       </c>
       <c r="Q41">
-        <v>8.787594110000001</v>
+        <v>8.768769599999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1178780775363193</v>
+        <v>0.1188582384208153</v>
       </c>
       <c r="T41">
-        <v>0.8634767961329357</v>
+        <v>0.8752188709657855</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.929855333585893</v>
+        <v>7.731608950246247</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0869369430524892</v>
+        <v>0.08697624880782359</v>
       </c>
       <c r="C42">
-        <v>32.22233598205058</v>
+        <v>31.72663767587428</v>
       </c>
       <c r="D42">
-        <v>40.50233598205058</v>
+        <v>40.48863767587429</v>
       </c>
       <c r="E42">
-        <v>-3.52</v>
+        <v>-3.037999999999997</v>
       </c>
       <c r="F42">
-        <v>19.28</v>
+        <v>19.762</v>
       </c>
       <c r="G42">
         <v>11</v>
@@ -4731,45 +4731,45 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M42">
-        <v>1.03148</v>
+        <v>1.0730766</v>
       </c>
       <c r="N42">
-        <v>6.943519999999999</v>
+        <v>6.901923399999998</v>
       </c>
       <c r="O42">
-        <v>1.8747504</v>
+        <v>1.863519318</v>
       </c>
       <c r="P42">
-        <v>5.068769599999999</v>
+        <v>5.038404081999999</v>
       </c>
       <c r="Q42">
-        <v>8.768769599999999</v>
+        <v>8.738404081999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1188582384208153</v>
+        <v>0.1198716250980061</v>
       </c>
       <c r="T42">
-        <v>0.8752188709657855</v>
+        <v>0.8873589822336472</v>
       </c>
       <c r="U42">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.27</v>
       </c>
       <c r="W42">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>7.731608950246247</v>
+        <v>7.431901879138914</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08697624880782359</v>
+        <v>0.08678195456315799</v>
       </c>
       <c r="C43">
-        <v>31.72663767587428</v>
+        <v>31.31244091204087</v>
       </c>
       <c r="D43">
-        <v>40.48863767587429</v>
+        <v>40.55644091204088</v>
       </c>
       <c r="E43">
-        <v>-3.037999999999997</v>
+        <v>-2.555999999999997</v>
       </c>
       <c r="F43">
-        <v>19.762</v>
+        <v>20.244</v>
       </c>
       <c r="G43">
         <v>11</v>
@@ -4813,28 +4813,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M43">
-        <v>1.0730766</v>
+        <v>1.0992492</v>
       </c>
       <c r="N43">
-        <v>6.901923399999998</v>
+        <v>6.875750799999999</v>
       </c>
       <c r="O43">
-        <v>1.863519318</v>
+        <v>1.856452716</v>
       </c>
       <c r="P43">
-        <v>5.038404081999999</v>
+        <v>5.019298083999999</v>
       </c>
       <c r="Q43">
-        <v>8.738404081999999</v>
+        <v>8.719298083999998</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1198716250980061</v>
+        <v>0.1209199561433758</v>
       </c>
       <c r="T43">
-        <v>0.8873589822336472</v>
+        <v>0.8999177180279869</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.431901879138914</v>
+        <v>7.254951834397511</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.086781954563158</v>
+        <v>0.08658766031849238</v>
       </c>
       <c r="C44">
-        <v>31.31244091204087</v>
+        <v>30.89847161896101</v>
       </c>
       <c r="D44">
-        <v>40.55644091204087</v>
+        <v>40.62447161896102</v>
       </c>
       <c r="E44">
-        <v>-2.556000000000001</v>
+        <v>-2.073999999999998</v>
       </c>
       <c r="F44">
-        <v>20.244</v>
+        <v>20.726</v>
       </c>
       <c r="G44">
         <v>11</v>
@@ -4895,28 +4895,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M44">
-        <v>1.0992492</v>
+        <v>1.1254218</v>
       </c>
       <c r="N44">
-        <v>6.875750799999999</v>
+        <v>6.849578199999998</v>
       </c>
       <c r="O44">
-        <v>1.856452716</v>
+        <v>1.849386114</v>
       </c>
       <c r="P44">
-        <v>5.019298083999999</v>
+        <v>5.000192085999998</v>
       </c>
       <c r="Q44">
-        <v>8.719298083999998</v>
+        <v>8.700192085999998</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1209199561433758</v>
+        <v>0.1220050707341971</v>
       </c>
       <c r="T44">
-        <v>0.8999177180279867</v>
+        <v>0.9129171112186191</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.254951834397513</v>
+        <v>7.086232024295243</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08658766031849238</v>
+        <v>0.08639336607382676</v>
       </c>
       <c r="C45">
-        <v>30.89847161896101</v>
+        <v>30.48473094325885</v>
       </c>
       <c r="D45">
-        <v>40.62447161896102</v>
+        <v>40.69273094325885</v>
       </c>
       <c r="E45">
-        <v>-2.073999999999998</v>
+        <v>-1.591999999999999</v>
       </c>
       <c r="F45">
-        <v>20.726</v>
+        <v>21.208</v>
       </c>
       <c r="G45">
         <v>11</v>
@@ -4977,28 +4977,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M45">
-        <v>1.1254218</v>
+        <v>1.1515944</v>
       </c>
       <c r="N45">
-        <v>6.849578199999998</v>
+        <v>6.823405599999999</v>
       </c>
       <c r="O45">
-        <v>1.849386114</v>
+        <v>1.842319512</v>
       </c>
       <c r="P45">
-        <v>5.000192085999998</v>
+        <v>4.981086088</v>
       </c>
       <c r="Q45">
-        <v>8.700192085999998</v>
+        <v>8.681086088000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1220050707341971</v>
+        <v>0.1231289394175478</v>
       </c>
       <c r="T45">
-        <v>0.9129171112186191</v>
+        <v>0.9263807684517739</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.086232024295243</v>
+        <v>6.925181296470353</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08639336607382676</v>
+        <v>0.08619907182916117</v>
       </c>
       <c r="C46">
-        <v>30.48473094325885</v>
+        <v>30.07122003927795</v>
       </c>
       <c r="D46">
-        <v>40.69273094325885</v>
+        <v>40.76122003927795</v>
       </c>
       <c r="E46">
-        <v>-1.591999999999999</v>
+        <v>-1.109999999999999</v>
       </c>
       <c r="F46">
-        <v>21.208</v>
+        <v>21.69</v>
       </c>
       <c r="G46">
         <v>11</v>
@@ -5059,28 +5059,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M46">
-        <v>1.1515944</v>
+        <v>1.177767</v>
       </c>
       <c r="N46">
-        <v>6.823405599999999</v>
+        <v>6.797232999999999</v>
       </c>
       <c r="O46">
-        <v>1.842319512</v>
+        <v>1.83525291</v>
       </c>
       <c r="P46">
-        <v>4.981086088</v>
+        <v>4.961980089999999</v>
       </c>
       <c r="Q46">
-        <v>8.681086088000001</v>
+        <v>8.66198009</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1231289394175478</v>
+        <v>0.1242936760530203</v>
       </c>
       <c r="T46">
-        <v>0.9263807684517739</v>
+        <v>0.9403340132206798</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.925181296470353</v>
+        <v>6.771288378771012</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08619907182916117</v>
+        <v>0.08600477758449557</v>
       </c>
       <c r="C47">
-        <v>30.07122003927795</v>
+        <v>29.6579400691464</v>
       </c>
       <c r="D47">
-        <v>40.76122003927795</v>
+        <v>40.8299400691464</v>
       </c>
       <c r="E47">
-        <v>-1.109999999999999</v>
+        <v>-0.6280000000000001</v>
       </c>
       <c r="F47">
-        <v>21.69</v>
+        <v>22.172</v>
       </c>
       <c r="G47">
         <v>11</v>
@@ -5141,28 +5141,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M47">
-        <v>1.177767</v>
+        <v>1.2039396</v>
       </c>
       <c r="N47">
-        <v>6.797232999999999</v>
+        <v>6.771060399999999</v>
       </c>
       <c r="O47">
-        <v>1.83525291</v>
+        <v>1.828186308</v>
       </c>
       <c r="P47">
-        <v>4.961980089999999</v>
+        <v>4.942874091999998</v>
       </c>
       <c r="Q47">
-        <v>8.66198009</v>
+        <v>8.642874092</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1242936760530203</v>
+        <v>0.1255015510823992</v>
       </c>
       <c r="T47">
-        <v>0.9403340132206798</v>
+        <v>0.9548040448328786</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.771288378771012</v>
+        <v>6.624086457493381</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08600477758449557</v>
+        <v>0.08581048333982995</v>
       </c>
       <c r="C48">
-        <v>29.6579400691464</v>
+        <v>29.24489220284256</v>
       </c>
       <c r="D48">
-        <v>40.8299400691464</v>
+        <v>40.89889220284256</v>
       </c>
       <c r="E48">
-        <v>-0.6280000000000001</v>
+        <v>-0.1459999999999972</v>
       </c>
       <c r="F48">
-        <v>22.172</v>
+        <v>22.654</v>
       </c>
       <c r="G48">
         <v>11</v>
@@ -5223,28 +5223,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M48">
-        <v>1.2039396</v>
+        <v>1.2301122</v>
       </c>
       <c r="N48">
-        <v>6.771060399999999</v>
+        <v>6.744887799999999</v>
       </c>
       <c r="O48">
-        <v>1.828186308</v>
+        <v>1.821119706</v>
       </c>
       <c r="P48">
-        <v>4.942874091999998</v>
+        <v>4.923768093999999</v>
       </c>
       <c r="Q48">
-        <v>8.642874092</v>
+        <v>8.623768093999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1255015510823992</v>
+        <v>0.1267550063015659</v>
       </c>
       <c r="T48">
-        <v>0.9548040448328786</v>
+        <v>0.9698201153738395</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.624086457493381</v>
+        <v>6.483148447759479</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08581048333982995</v>
+        <v>0.08561618909516434</v>
       </c>
       <c r="C49">
-        <v>29.24489220284256</v>
+        <v>28.83207761826135</v>
       </c>
       <c r="D49">
-        <v>40.89889220284256</v>
+        <v>40.96807761826135</v>
       </c>
       <c r="E49">
-        <v>-0.1459999999999972</v>
+        <v>0.3360000000000021</v>
       </c>
       <c r="F49">
-        <v>22.654</v>
+        <v>23.136</v>
       </c>
       <c r="G49">
         <v>11</v>
@@ -5305,28 +5305,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M49">
-        <v>1.2301122</v>
+        <v>1.2562848</v>
       </c>
       <c r="N49">
-        <v>6.744887799999999</v>
+        <v>6.718715199999998</v>
       </c>
       <c r="O49">
-        <v>1.821119706</v>
+        <v>1.814053104</v>
       </c>
       <c r="P49">
-        <v>4.923768093999999</v>
+        <v>4.904662095999999</v>
       </c>
       <c r="Q49">
-        <v>8.623768093999999</v>
+        <v>8.604662095999998</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1267550063015659</v>
+        <v>0.1280566713368545</v>
       </c>
       <c r="T49">
-        <v>0.9698201153738395</v>
+        <v>0.9854137270894529</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.483148447759479</v>
+        <v>6.348082855097823</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08561618909516434</v>
+        <v>0.08542189485049873</v>
       </c>
       <c r="C50">
-        <v>28.83207761826135</v>
+        <v>28.41949750128148</v>
       </c>
       <c r="D50">
-        <v>40.96807761826135</v>
+        <v>41.03749750128149</v>
       </c>
       <c r="E50">
-        <v>0.3359999999999985</v>
+        <v>0.8180000000000014</v>
       </c>
       <c r="F50">
-        <v>23.136</v>
+        <v>23.618</v>
       </c>
       <c r="G50">
         <v>11</v>
@@ -5387,28 +5387,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M50">
-        <v>1.2562848</v>
+        <v>1.2824574</v>
       </c>
       <c r="N50">
-        <v>6.718715199999998</v>
+        <v>6.692542599999999</v>
       </c>
       <c r="O50">
-        <v>1.814053104</v>
+        <v>1.806986502</v>
       </c>
       <c r="P50">
-        <v>4.904662095999999</v>
+        <v>4.885556097999999</v>
       </c>
       <c r="Q50">
-        <v>8.604662095999998</v>
+        <v>8.585556097999998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1280566713368545</v>
+        <v>0.1294093820598014</v>
       </c>
       <c r="T50">
-        <v>0.9854137270894529</v>
+        <v>1.001618852989992</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.348082855097823</v>
+        <v>6.218530143769296</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08542189485049873</v>
+        <v>0.08559260060583312</v>
       </c>
       <c r="C51">
-        <v>28.41949750128148</v>
+        <v>27.87649308073134</v>
       </c>
       <c r="D51">
-        <v>41.03749750128149</v>
+        <v>40.97649308073134</v>
       </c>
       <c r="E51">
-        <v>0.8180000000000014</v>
+        <v>1.300000000000001</v>
       </c>
       <c r="F51">
-        <v>23.618</v>
+        <v>24.1</v>
       </c>
       <c r="G51">
         <v>11</v>
@@ -5469,45 +5469,45 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M51">
-        <v>1.2824574</v>
+        <v>1.33273</v>
       </c>
       <c r="N51">
-        <v>6.692542599999999</v>
+        <v>6.642269999999998</v>
       </c>
       <c r="O51">
-        <v>1.806986502</v>
+        <v>1.7934129</v>
       </c>
       <c r="P51">
-        <v>4.885556097999999</v>
+        <v>4.848857099999998</v>
       </c>
       <c r="Q51">
-        <v>8.585556097999998</v>
+        <v>8.548857099999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1294093820598014</v>
+        <v>0.1308162012116663</v>
       </c>
       <c r="T51">
-        <v>1.001618852989992</v>
+        <v>1.018472183926553</v>
       </c>
       <c r="U51">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V51">
         <v>0.27</v>
       </c>
       <c r="W51">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>6.218530143769296</v>
+        <v>5.983957740877745</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08559260060583312</v>
+        <v>0.08540560636116754</v>
       </c>
       <c r="C52">
-        <v>27.87649308073134</v>
+        <v>27.46132794666018</v>
       </c>
       <c r="D52">
-        <v>40.97649308073134</v>
+        <v>41.04332794666018</v>
       </c>
       <c r="E52">
-        <v>1.300000000000001</v>
+        <v>1.782</v>
       </c>
       <c r="F52">
-        <v>24.1</v>
+        <v>24.582</v>
       </c>
       <c r="G52">
         <v>11</v>
@@ -5551,28 +5551,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M52">
-        <v>1.33273</v>
+        <v>1.3593846</v>
       </c>
       <c r="N52">
-        <v>6.642269999999998</v>
+        <v>6.615615399999998</v>
       </c>
       <c r="O52">
-        <v>1.7934129</v>
+        <v>1.786216158</v>
       </c>
       <c r="P52">
-        <v>4.848857099999998</v>
+        <v>4.829399241999999</v>
       </c>
       <c r="Q52">
-        <v>8.548857099999999</v>
+        <v>8.529399242</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1308162012116663</v>
+        <v>0.1322804415534031</v>
       </c>
       <c r="T52">
-        <v>1.018472183926553</v>
+        <v>1.036013405921749</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.983957740877745</v>
+        <v>5.866625236154653</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08540560636116754</v>
+        <v>0.08521861211650193</v>
       </c>
       <c r="C53">
-        <v>27.46132794666018</v>
+        <v>27.04638119130437</v>
       </c>
       <c r="D53">
-        <v>41.04332794666018</v>
+        <v>41.11038119130438</v>
       </c>
       <c r="E53">
-        <v>1.782</v>
+        <v>2.264000000000003</v>
       </c>
       <c r="F53">
-        <v>24.582</v>
+        <v>25.064</v>
       </c>
       <c r="G53">
         <v>11</v>
@@ -5633,28 +5633,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M53">
-        <v>1.3593846</v>
+        <v>1.3860392</v>
       </c>
       <c r="N53">
-        <v>6.615615399999998</v>
+        <v>6.588960799999999</v>
       </c>
       <c r="O53">
-        <v>1.786216158</v>
+        <v>1.779019416</v>
       </c>
       <c r="P53">
-        <v>4.829399241999999</v>
+        <v>4.809941383999999</v>
       </c>
       <c r="Q53">
-        <v>8.529399242</v>
+        <v>8.509941383999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1322804415534031</v>
+        <v>0.133805691909379</v>
       </c>
       <c r="T53">
-        <v>1.036013405921749</v>
+        <v>1.054285512166745</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.866625236154653</v>
+        <v>5.753805520074756</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08521861211650193</v>
+        <v>0.08503161787183632</v>
       </c>
       <c r="C54">
-        <v>27.04638119130437</v>
+        <v>26.63165388672346</v>
       </c>
       <c r="D54">
-        <v>41.11038119130438</v>
+        <v>41.17765388672346</v>
       </c>
       <c r="E54">
-        <v>2.264000000000003</v>
+        <v>2.746000000000002</v>
       </c>
       <c r="F54">
-        <v>25.064</v>
+        <v>25.546</v>
       </c>
       <c r="G54">
         <v>11</v>
@@ -5715,28 +5715,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M54">
-        <v>1.3860392</v>
+        <v>1.4126938</v>
       </c>
       <c r="N54">
-        <v>6.588960799999999</v>
+        <v>6.562306199999998</v>
       </c>
       <c r="O54">
-        <v>1.779019416</v>
+        <v>1.771822674</v>
       </c>
       <c r="P54">
-        <v>4.809941383999999</v>
+        <v>4.790483525999999</v>
       </c>
       <c r="Q54">
-        <v>8.509941383999999</v>
+        <v>8.490483525999998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.133805691909379</v>
+        <v>0.135395846535822</v>
       </c>
       <c r="T54">
-        <v>1.054285512166745</v>
+        <v>1.073335154847698</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.753805520074756</v>
+        <v>5.645243151771457</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08503161787183632</v>
+        <v>0.0848446236271707</v>
       </c>
       <c r="C55">
-        <v>26.63165388672346</v>
+        <v>26.21714711200564</v>
       </c>
       <c r="D55">
-        <v>41.17765388672346</v>
+        <v>41.24514711200565</v>
       </c>
       <c r="E55">
-        <v>2.746000000000002</v>
+        <v>3.228000000000002</v>
       </c>
       <c r="F55">
-        <v>25.546</v>
+        <v>26.028</v>
       </c>
       <c r="G55">
         <v>11</v>
@@ -5797,28 +5797,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M55">
-        <v>1.4126938</v>
+        <v>1.4393484</v>
       </c>
       <c r="N55">
-        <v>6.562306199999998</v>
+        <v>6.535651599999999</v>
       </c>
       <c r="O55">
-        <v>1.771822674</v>
+        <v>1.764625932</v>
       </c>
       <c r="P55">
-        <v>4.790483525999999</v>
+        <v>4.771025667999999</v>
       </c>
       <c r="Q55">
-        <v>8.490483525999998</v>
+        <v>8.471025667999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.135395846535822</v>
+        <v>0.1370551383199363</v>
       </c>
       <c r="T55">
-        <v>1.073335154847698</v>
+        <v>1.093213042862606</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.645243151771457</v>
+        <v>5.540701611923839</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0848446236271707</v>
+        <v>0.0846576293825051</v>
       </c>
       <c r="C56">
-        <v>26.21714711200564</v>
+        <v>25.8028619533256</v>
       </c>
       <c r="D56">
-        <v>41.24514711200565</v>
+        <v>41.31286195332561</v>
       </c>
       <c r="E56">
-        <v>3.228000000000002</v>
+        <v>3.710000000000004</v>
       </c>
       <c r="F56">
-        <v>26.028</v>
+        <v>26.51000000000001</v>
       </c>
       <c r="G56">
         <v>11</v>
@@ -5879,28 +5879,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M56">
-        <v>1.4393484</v>
+        <v>1.466003</v>
       </c>
       <c r="N56">
-        <v>6.535651599999999</v>
+        <v>6.508996999999998</v>
       </c>
       <c r="O56">
-        <v>1.764625932</v>
+        <v>1.75742919</v>
       </c>
       <c r="P56">
-        <v>4.771025667999999</v>
+        <v>4.751567809999998</v>
       </c>
       <c r="Q56">
-        <v>8.471025667999999</v>
+        <v>8.451567809999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1370551383199363</v>
+        <v>0.1387881764055669</v>
       </c>
       <c r="T56">
-        <v>1.093213042862606</v>
+        <v>1.113974392567065</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.540701611923839</v>
+        <v>5.439961582616132</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0846576293825051</v>
+        <v>0.08447063513783949</v>
       </c>
       <c r="C57">
-        <v>25.8028619533256</v>
+        <v>25.3887995040027</v>
       </c>
       <c r="D57">
-        <v>41.31286195332561</v>
+        <v>41.3807995040027</v>
       </c>
       <c r="E57">
-        <v>3.710000000000004</v>
+        <v>4.192000000000004</v>
       </c>
       <c r="F57">
-        <v>26.51000000000001</v>
+        <v>26.992</v>
       </c>
       <c r="G57">
         <v>11</v>
@@ -5961,28 +5961,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M57">
-        <v>1.466003</v>
+        <v>1.4926576</v>
       </c>
       <c r="N57">
-        <v>6.508996999999998</v>
+        <v>6.482342399999999</v>
       </c>
       <c r="O57">
-        <v>1.75742919</v>
+        <v>1.750232448</v>
       </c>
       <c r="P57">
-        <v>4.751567809999998</v>
+        <v>4.732109951999998</v>
       </c>
       <c r="Q57">
-        <v>8.451567809999998</v>
+        <v>8.432109951999998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1387881764055669</v>
+        <v>0.1405999889496352</v>
       </c>
       <c r="T57">
-        <v>1.113974392567065</v>
+        <v>1.135679439985363</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.439961582616132</v>
+        <v>5.342819411497987</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08447063513783949</v>
+        <v>0.08428364089317389</v>
       </c>
       <c r="C58">
-        <v>25.3887995040027</v>
+        <v>24.97496086455988</v>
       </c>
       <c r="D58">
-        <v>41.3807995040027</v>
+        <v>41.44896086455988</v>
       </c>
       <c r="E58">
-        <v>4.192000000000004</v>
+        <v>4.674000000000003</v>
       </c>
       <c r="F58">
-        <v>26.992</v>
+        <v>27.474</v>
       </c>
       <c r="G58">
         <v>11</v>
@@ -6043,28 +6043,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M58">
-        <v>1.4926576</v>
+        <v>1.5193122</v>
       </c>
       <c r="N58">
-        <v>6.482342399999999</v>
+        <v>6.455687799999998</v>
       </c>
       <c r="O58">
-        <v>1.750232448</v>
+        <v>1.743035705999999</v>
       </c>
       <c r="P58">
-        <v>4.732109951999998</v>
+        <v>4.712652093999998</v>
       </c>
       <c r="Q58">
-        <v>8.432109951999998</v>
+        <v>8.412652093999998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1405999889496352</v>
+        <v>0.1424960718445905</v>
       </c>
       <c r="T58">
-        <v>1.135679439985363</v>
+        <v>1.158394024492885</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.342819411497987</v>
+        <v>5.249085737612057</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08428364089317389</v>
+        <v>0.08409664664850829</v>
       </c>
       <c r="C59">
-        <v>24.97496086455988</v>
+        <v>24.56134714278301</v>
       </c>
       <c r="D59">
-        <v>41.44896086455988</v>
+        <v>41.51734714278302</v>
       </c>
       <c r="E59">
-        <v>4.674000000000003</v>
+        <v>5.156000000000006</v>
       </c>
       <c r="F59">
-        <v>27.474</v>
+        <v>27.95600000000001</v>
       </c>
       <c r="G59">
         <v>11</v>
@@ -6125,28 +6125,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M59">
-        <v>1.5193122</v>
+        <v>1.5459668</v>
       </c>
       <c r="N59">
-        <v>6.455687799999998</v>
+        <v>6.429033199999998</v>
       </c>
       <c r="O59">
-        <v>1.743035705999999</v>
+        <v>1.735838964</v>
       </c>
       <c r="P59">
-        <v>4.712652093999998</v>
+        <v>4.693194235999998</v>
       </c>
       <c r="Q59">
-        <v>8.412652093999998</v>
+        <v>8.393194235999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1424960718445905</v>
+        <v>0.1444824444012102</v>
       </c>
       <c r="T59">
-        <v>1.158394024492885</v>
+        <v>1.182190255881716</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.249085737612057</v>
+        <v>5.158584259377366</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08409664664850829</v>
+        <v>0.08390965240384268</v>
       </c>
       <c r="C60">
-        <v>24.56134714278302</v>
+        <v>24.14795945378099</v>
       </c>
       <c r="D60">
-        <v>41.51734714278302</v>
+        <v>41.58595945378099</v>
       </c>
       <c r="E60">
-        <v>5.155999999999999</v>
+        <v>5.637999999999998</v>
       </c>
       <c r="F60">
-        <v>27.956</v>
+        <v>28.438</v>
       </c>
       <c r="G60">
         <v>11</v>
@@ -6207,28 +6207,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M60">
-        <v>1.5459668</v>
+        <v>1.5726214</v>
       </c>
       <c r="N60">
-        <v>6.429033199999999</v>
+        <v>6.402378599999999</v>
       </c>
       <c r="O60">
-        <v>1.735838964</v>
+        <v>1.728642222</v>
       </c>
       <c r="P60">
-        <v>4.693194235999999</v>
+        <v>4.673736377999999</v>
       </c>
       <c r="Q60">
-        <v>8.393194235999999</v>
+        <v>8.373736378</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1444824444012102</v>
+        <v>0.1465657131801041</v>
       </c>
       <c r="T60">
-        <v>1.182190255881716</v>
+        <v>1.207147279045613</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.158584259377368</v>
+        <v>5.071150627862496</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08390965240384268</v>
+        <v>0.08372265815917707</v>
       </c>
       <c r="C61">
-        <v>24.14795945378099</v>
+        <v>23.73479892004629</v>
       </c>
       <c r="D61">
-        <v>41.58595945378099</v>
+        <v>41.6547989200463</v>
       </c>
       <c r="E61">
-        <v>5.637999999999998</v>
+        <v>6.120000000000001</v>
       </c>
       <c r="F61">
-        <v>28.438</v>
+        <v>28.92</v>
       </c>
       <c r="G61">
         <v>11</v>
@@ -6289,28 +6289,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M61">
-        <v>1.5726214</v>
+        <v>1.599276</v>
       </c>
       <c r="N61">
-        <v>6.402378599999999</v>
+        <v>6.375723999999998</v>
       </c>
       <c r="O61">
-        <v>1.728642222</v>
+        <v>1.72144548</v>
       </c>
       <c r="P61">
-        <v>4.673736377999999</v>
+        <v>4.654278519999998</v>
       </c>
       <c r="Q61">
-        <v>8.373736378</v>
+        <v>8.354278519999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1465657131801041</v>
+        <v>0.1487531453979427</v>
       </c>
       <c r="T61">
-        <v>1.207147279045613</v>
+        <v>1.233352153367704</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.071150627862496</v>
+        <v>4.986631450731455</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08372265815917707</v>
+        <v>0.08353566391451148</v>
       </c>
       <c r="C62">
-        <v>23.73479892004629</v>
+        <v>23.32186667151621</v>
       </c>
       <c r="D62">
-        <v>41.6547989200463</v>
+        <v>41.72386667151621</v>
       </c>
       <c r="E62">
-        <v>6.120000000000001</v>
+        <v>6.602</v>
       </c>
       <c r="F62">
-        <v>28.92</v>
+        <v>29.402</v>
       </c>
       <c r="G62">
         <v>11</v>
@@ -6371,28 +6371,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M62">
-        <v>1.599276</v>
+        <v>1.6259306</v>
       </c>
       <c r="N62">
-        <v>6.375723999999998</v>
+        <v>6.349069399999999</v>
       </c>
       <c r="O62">
-        <v>1.72144548</v>
+        <v>1.714248738</v>
       </c>
       <c r="P62">
-        <v>4.654278519999998</v>
+        <v>4.634820661999999</v>
       </c>
       <c r="Q62">
-        <v>8.354278519999998</v>
+        <v>8.334820661999998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1487531453979427</v>
+        <v>0.1510527536269525</v>
       </c>
       <c r="T62">
-        <v>1.233352153367704</v>
+        <v>1.260900867398621</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.986631450731455</v>
+        <v>4.904883394162087</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08353566391451148</v>
+        <v>0.08334866966984586</v>
       </c>
       <c r="C63">
-        <v>23.32186667151621</v>
+        <v>22.90916384563467</v>
       </c>
       <c r="D63">
-        <v>41.72386667151621</v>
+        <v>41.79316384563467</v>
       </c>
       <c r="E63">
-        <v>6.602</v>
+        <v>7.084</v>
       </c>
       <c r="F63">
-        <v>29.402</v>
+        <v>29.884</v>
       </c>
       <c r="G63">
         <v>11</v>
@@ -6453,28 +6453,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M63">
-        <v>1.6259306</v>
+        <v>1.6525852</v>
       </c>
       <c r="N63">
-        <v>6.349069399999999</v>
+        <v>6.322414799999999</v>
       </c>
       <c r="O63">
-        <v>1.714248738</v>
+        <v>1.707051996</v>
       </c>
       <c r="P63">
-        <v>4.634820661999999</v>
+        <v>4.615362803999999</v>
       </c>
       <c r="Q63">
-        <v>8.334820661999998</v>
+        <v>8.315362803999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1510527536269525</v>
+        <v>0.1534733938680154</v>
       </c>
       <c r="T63">
-        <v>1.260900867398621</v>
+        <v>1.289899513746955</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.904883394162087</v>
+        <v>4.825772371675601</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08334866966984586</v>
+        <v>0.08316167542518024</v>
       </c>
       <c r="C64">
-        <v>22.90916384563467</v>
+        <v>22.49669158741468</v>
       </c>
       <c r="D64">
-        <v>41.79316384563467</v>
+        <v>41.86269158741469</v>
       </c>
       <c r="E64">
-        <v>7.084</v>
+        <v>7.566000000000003</v>
       </c>
       <c r="F64">
-        <v>29.884</v>
+        <v>30.366</v>
       </c>
       <c r="G64">
         <v>11</v>
@@ -6535,28 +6535,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M64">
-        <v>1.6525852</v>
+        <v>1.6792398</v>
       </c>
       <c r="N64">
-        <v>6.322414799999999</v>
+        <v>6.295760199999998</v>
       </c>
       <c r="O64">
-        <v>1.707051996</v>
+        <v>1.699855254</v>
       </c>
       <c r="P64">
-        <v>4.615362803999999</v>
+        <v>4.595904945999999</v>
       </c>
       <c r="Q64">
-        <v>8.315362803999999</v>
+        <v>8.295904946</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1534733938680154</v>
+        <v>0.1560248795275142</v>
       </c>
       <c r="T64">
-        <v>1.289899513746955</v>
+        <v>1.320465654492496</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.825772371675601</v>
+        <v>4.749172810220433</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08316167542518024</v>
+        <v>0.08297468118051465</v>
       </c>
       <c r="C65">
-        <v>22.49669158741468</v>
+        <v>22.08445104950136</v>
       </c>
       <c r="D65">
-        <v>41.86269158741469</v>
+        <v>41.93245104950137</v>
       </c>
       <c r="E65">
-        <v>7.566000000000003</v>
+        <v>8.048000000000002</v>
       </c>
       <c r="F65">
-        <v>30.366</v>
+        <v>30.848</v>
       </c>
       <c r="G65">
         <v>11</v>
@@ -6617,28 +6617,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M65">
-        <v>1.6792398</v>
+        <v>1.7058944</v>
       </c>
       <c r="N65">
-        <v>6.295760199999998</v>
+        <v>6.269105599999999</v>
       </c>
       <c r="O65">
-        <v>1.699855254</v>
+        <v>1.692658512</v>
       </c>
       <c r="P65">
-        <v>4.595904945999999</v>
+        <v>4.576447087999999</v>
       </c>
       <c r="Q65">
-        <v>8.295904946</v>
+        <v>8.276447087999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1560248795275142</v>
+        <v>0.1587181143903185</v>
       </c>
       <c r="T65">
-        <v>1.320465654492496</v>
+        <v>1.352729914168344</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.749172810220433</v>
+        <v>4.674966985060738</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08297468118051465</v>
+        <v>0.08278768693584904</v>
       </c>
       <c r="C66">
-        <v>22.08445104950136</v>
+        <v>21.67244339223572</v>
       </c>
       <c r="D66">
-        <v>41.93245104950137</v>
+        <v>42.00244339223572</v>
       </c>
       <c r="E66">
-        <v>8.048000000000002</v>
+        <v>8.530000000000001</v>
       </c>
       <c r="F66">
-        <v>30.848</v>
+        <v>31.33</v>
       </c>
       <c r="G66">
         <v>11</v>
@@ -6699,28 +6699,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M66">
-        <v>1.7058944</v>
+        <v>1.732549</v>
       </c>
       <c r="N66">
-        <v>6.269105599999999</v>
+        <v>6.242450999999999</v>
       </c>
       <c r="O66">
-        <v>1.692658512</v>
+        <v>1.68546177</v>
       </c>
       <c r="P66">
-        <v>4.576447087999999</v>
+        <v>4.556989229999999</v>
       </c>
       <c r="Q66">
-        <v>8.276447087999999</v>
+        <v>8.256989229999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1587181143903185</v>
+        <v>0.1615652483881401</v>
       </c>
       <c r="T66">
-        <v>1.352729914168344</v>
+        <v>1.38683784582567</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.674966985060738</v>
+        <v>4.603044416059805</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08278768693584904</v>
+        <v>0.08260069269118343</v>
       </c>
       <c r="C67">
-        <v>21.67244339223572</v>
+        <v>21.2606697837189</v>
       </c>
       <c r="D67">
-        <v>42.00244339223572</v>
+        <v>42.0726697837189</v>
       </c>
       <c r="E67">
-        <v>8.530000000000001</v>
+        <v>9.012000000000004</v>
       </c>
       <c r="F67">
-        <v>31.33</v>
+        <v>31.812</v>
       </c>
       <c r="G67">
         <v>11</v>
@@ -6781,28 +6781,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M67">
-        <v>1.732549</v>
+        <v>1.7592036</v>
       </c>
       <c r="N67">
-        <v>6.242450999999999</v>
+        <v>6.215796399999999</v>
       </c>
       <c r="O67">
-        <v>1.68546177</v>
+        <v>1.678265028</v>
       </c>
       <c r="P67">
-        <v>4.556989229999999</v>
+        <v>4.537531371999998</v>
       </c>
       <c r="Q67">
-        <v>8.256989229999999</v>
+        <v>8.237531371999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1615652483881401</v>
+        <v>0.1645798608564219</v>
       </c>
       <c r="T67">
-        <v>1.38683784582567</v>
+        <v>1.422952126404015</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.603044416059805</v>
+        <v>4.533301318846776</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08260069269118343</v>
+        <v>0.08363644844651782</v>
       </c>
       <c r="C68">
-        <v>21.2606697837189</v>
+        <v>20.39261270445617</v>
       </c>
       <c r="D68">
-        <v>42.0726697837189</v>
+        <v>41.68661270445617</v>
       </c>
       <c r="E68">
-        <v>9.012000000000004</v>
+        <v>9.494000000000003</v>
       </c>
       <c r="F68">
-        <v>31.812</v>
+        <v>32.294</v>
       </c>
       <c r="G68">
         <v>11</v>
@@ -6863,45 +6863,45 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M68">
-        <v>1.7592036</v>
+        <v>1.8665932</v>
       </c>
       <c r="N68">
-        <v>6.215796399999999</v>
+        <v>6.108406799999998</v>
       </c>
       <c r="O68">
-        <v>1.678265028</v>
+        <v>1.649269836</v>
       </c>
       <c r="P68">
-        <v>4.537531371999998</v>
+        <v>4.459136963999999</v>
       </c>
       <c r="Q68">
-        <v>8.237531371999999</v>
+        <v>8.159136963999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1645798608564219</v>
+        <v>0.1677771771106601</v>
       </c>
       <c r="T68">
-        <v>1.422952126404015</v>
+        <v>1.461255151259835</v>
       </c>
       <c r="U68">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V68">
         <v>0.27</v>
       </c>
       <c r="W68">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>4.533301318846776</v>
+        <v>4.272489581554244</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08363644844651782</v>
+        <v>0.08346770420185223</v>
       </c>
       <c r="C69">
-        <v>20.39261270445617</v>
+        <v>19.97302489122915</v>
       </c>
       <c r="D69">
-        <v>41.68661270445617</v>
+        <v>41.74902489122915</v>
       </c>
       <c r="E69">
-        <v>9.494000000000003</v>
+        <v>9.976000000000003</v>
       </c>
       <c r="F69">
-        <v>32.294</v>
+        <v>32.776</v>
       </c>
       <c r="G69">
         <v>11</v>
@@ -6945,28 +6945,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M69">
-        <v>1.8665932</v>
+        <v>1.8944528</v>
       </c>
       <c r="N69">
-        <v>6.108406799999998</v>
+        <v>6.080547199999998</v>
       </c>
       <c r="O69">
-        <v>1.649269836</v>
+        <v>1.641747744</v>
       </c>
       <c r="P69">
-        <v>4.459136963999999</v>
+        <v>4.438799455999998</v>
       </c>
       <c r="Q69">
-        <v>8.159136963999998</v>
+        <v>8.138799455999997</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1677771771106601</v>
+        <v>0.1711743256307882</v>
       </c>
       <c r="T69">
-        <v>1.461255151259835</v>
+        <v>1.501952115169144</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.272489581554244</v>
+        <v>4.209658852413741</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08346770420185223</v>
+        <v>0.08329895995718661</v>
       </c>
       <c r="C70">
-        <v>19.97302489122915</v>
+        <v>19.5536242422484</v>
       </c>
       <c r="D70">
-        <v>41.74902489122915</v>
+        <v>41.81162424224841</v>
       </c>
       <c r="E70">
-        <v>9.976000000000003</v>
+        <v>10.458</v>
       </c>
       <c r="F70">
-        <v>32.776</v>
+        <v>33.258</v>
       </c>
       <c r="G70">
         <v>11</v>
@@ -7027,28 +7027,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M70">
-        <v>1.8944528</v>
+        <v>1.9223124</v>
       </c>
       <c r="N70">
-        <v>6.080547199999998</v>
+        <v>6.052687599999999</v>
       </c>
       <c r="O70">
-        <v>1.641747744</v>
+        <v>1.634225652</v>
       </c>
       <c r="P70">
-        <v>4.438799455999998</v>
+        <v>4.418461947999999</v>
       </c>
       <c r="Q70">
-        <v>8.138799455999997</v>
+        <v>8.118461948</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1711743256307882</v>
+        <v>0.1747906450231826</v>
       </c>
       <c r="T70">
-        <v>1.501952115169144</v>
+        <v>1.545274689653247</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.209658852413741</v>
+        <v>4.148649303828035</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08329895995718661</v>
+        <v>0.08313021571252101</v>
       </c>
       <c r="C71">
-        <v>19.5536242422484</v>
+        <v>19.13441160069199</v>
       </c>
       <c r="D71">
-        <v>41.81162424224841</v>
+        <v>41.87441160069199</v>
       </c>
       <c r="E71">
-        <v>10.458</v>
+        <v>10.94</v>
       </c>
       <c r="F71">
-        <v>33.258</v>
+        <v>33.74</v>
       </c>
       <c r="G71">
         <v>11</v>
@@ -7109,28 +7109,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M71">
-        <v>1.9223124</v>
+        <v>1.950172</v>
       </c>
       <c r="N71">
-        <v>6.052687599999999</v>
+        <v>6.024827999999999</v>
       </c>
       <c r="O71">
-        <v>1.634225652</v>
+        <v>1.62670356</v>
       </c>
       <c r="P71">
-        <v>4.418461947999999</v>
+        <v>4.398124439999998</v>
       </c>
       <c r="Q71">
-        <v>8.118461948</v>
+        <v>8.098124439999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1747906450231826</v>
+        <v>0.1786480523750701</v>
       </c>
       <c r="T71">
-        <v>1.545274689653247</v>
+        <v>1.591485435769624</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.148649303828035</v>
+        <v>4.089382885201919</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08313021571252101</v>
+        <v>0.0829614714678554</v>
       </c>
       <c r="C72">
-        <v>19.13441160069199</v>
+        <v>18.71538781481035</v>
       </c>
       <c r="D72">
-        <v>41.87441160069199</v>
+        <v>41.93738781481036</v>
       </c>
       <c r="E72">
-        <v>10.94</v>
+        <v>11.42200000000001</v>
       </c>
       <c r="F72">
-        <v>33.74</v>
+        <v>34.22200000000001</v>
       </c>
       <c r="G72">
         <v>11</v>
@@ -7191,28 +7191,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M72">
-        <v>1.950172</v>
+        <v>1.978031600000001</v>
       </c>
       <c r="N72">
-        <v>6.024827999999999</v>
+        <v>5.996968399999998</v>
       </c>
       <c r="O72">
-        <v>1.62670356</v>
+        <v>1.619181468</v>
       </c>
       <c r="P72">
-        <v>4.398124439999998</v>
+        <v>4.377786931999998</v>
       </c>
       <c r="Q72">
-        <v>8.098124439999999</v>
+        <v>8.077786931999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1786480523750701</v>
+        <v>0.1827714878201911</v>
       </c>
       <c r="T72">
-        <v>1.591485435769624</v>
+        <v>1.640883129894027</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.089382885201919</v>
+        <v>4.031785943156821</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0829614714678554</v>
+        <v>0.08463232722318981</v>
       </c>
       <c r="C73">
-        <v>18.71538781481036</v>
+        <v>17.61804151879979</v>
       </c>
       <c r="D73">
-        <v>41.93738781481036</v>
+        <v>41.32204151879979</v>
       </c>
       <c r="E73">
-        <v>11.422</v>
+        <v>11.904</v>
       </c>
       <c r="F73">
-        <v>34.222</v>
+        <v>34.704</v>
       </c>
       <c r="G73">
         <v>11</v>
@@ -7273,45 +7273,45 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M73">
-        <v>1.9780316</v>
+        <v>2.1273552</v>
       </c>
       <c r="N73">
-        <v>5.996968399999998</v>
+        <v>5.847644799999999</v>
       </c>
       <c r="O73">
-        <v>1.619181468</v>
+        <v>1.578864096</v>
       </c>
       <c r="P73">
-        <v>4.377786931999998</v>
+        <v>4.268780703999999</v>
       </c>
       <c r="Q73">
-        <v>8.077786931999999</v>
+        <v>7.968780703999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.182771487820191</v>
+        <v>0.187189454368535</v>
       </c>
       <c r="T73">
-        <v>1.640883129894026</v>
+        <v>1.6938092307416</v>
       </c>
       <c r="U73">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V73">
         <v>0.27</v>
       </c>
       <c r="W73">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>4.031785943156822</v>
+        <v>3.748786286370982</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08463232722318981</v>
+        <v>0.08448913297852419</v>
       </c>
       <c r="C74">
-        <v>17.61804151879979</v>
+        <v>17.18806903027993</v>
       </c>
       <c r="D74">
-        <v>41.32204151879979</v>
+        <v>41.37406903027993</v>
       </c>
       <c r="E74">
-        <v>11.904</v>
+        <v>12.386</v>
       </c>
       <c r="F74">
-        <v>34.704</v>
+        <v>35.186</v>
       </c>
       <c r="G74">
         <v>11</v>
@@ -7355,28 +7355,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M74">
-        <v>2.1273552</v>
+        <v>2.1569018</v>
       </c>
       <c r="N74">
-        <v>5.847644799999999</v>
+        <v>5.818098199999999</v>
       </c>
       <c r="O74">
-        <v>1.578864096</v>
+        <v>1.570886514</v>
       </c>
       <c r="P74">
-        <v>4.268780703999999</v>
+        <v>4.247211685999999</v>
       </c>
       <c r="Q74">
-        <v>7.968780703999999</v>
+        <v>7.947211685999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.187189454368535</v>
+        <v>0.1919346776982377</v>
       </c>
       <c r="T74">
-        <v>1.6938092307416</v>
+        <v>1.750655783503809</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.748786286370982</v>
+        <v>3.69743304957138</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08448913297852419</v>
+        <v>0.08434593873385859</v>
       </c>
       <c r="C75">
-        <v>17.18806903027993</v>
+        <v>16.75822771990556</v>
       </c>
       <c r="D75">
-        <v>41.37406903027993</v>
+        <v>41.42622771990555</v>
       </c>
       <c r="E75">
-        <v>12.386</v>
+        <v>12.868</v>
       </c>
       <c r="F75">
-        <v>35.186</v>
+        <v>35.668</v>
       </c>
       <c r="G75">
         <v>11</v>
@@ -7437,28 +7437,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M75">
-        <v>2.1569018</v>
+        <v>2.1864484</v>
       </c>
       <c r="N75">
-        <v>5.818098199999999</v>
+        <v>5.788551599999998</v>
       </c>
       <c r="O75">
-        <v>1.570886514</v>
+        <v>1.562908932</v>
       </c>
       <c r="P75">
-        <v>4.247211685999999</v>
+        <v>4.225642667999999</v>
       </c>
       <c r="Q75">
-        <v>7.947211685999999</v>
+        <v>7.925642667999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1919346776982377</v>
+        <v>0.1970449182071484</v>
       </c>
       <c r="T75">
-        <v>1.750655783503809</v>
+        <v>1.811875148016958</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.69743304957138</v>
+        <v>3.647467738090685</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08434593873385859</v>
+        <v>0.08420274448919297</v>
       </c>
       <c r="C76">
-        <v>16.75822771990556</v>
+        <v>16.32851808441653</v>
       </c>
       <c r="D76">
-        <v>41.42622771990555</v>
+        <v>41.47851808441654</v>
       </c>
       <c r="E76">
-        <v>12.868</v>
+        <v>13.35</v>
       </c>
       <c r="F76">
-        <v>35.668</v>
+        <v>36.15000000000001</v>
       </c>
       <c r="G76">
         <v>11</v>
@@ -7519,28 +7519,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M76">
-        <v>2.1864484</v>
+        <v>2.215995</v>
       </c>
       <c r="N76">
-        <v>5.788551599999998</v>
+        <v>5.759004999999998</v>
       </c>
       <c r="O76">
-        <v>1.562908932</v>
+        <v>1.55493135</v>
       </c>
       <c r="P76">
-        <v>4.225642667999999</v>
+        <v>4.204073649999999</v>
       </c>
       <c r="Q76">
-        <v>7.925642667999999</v>
+        <v>7.904073649999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1970449182071484</v>
+        <v>0.2025639779567719</v>
       </c>
       <c r="T76">
-        <v>1.811875148016958</v>
+        <v>1.877992061691159</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.647467738090685</v>
+        <v>3.598834834916143</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08420274448919297</v>
+        <v>0.08405955024452737</v>
       </c>
       <c r="C77">
-        <v>16.32851808441653</v>
+        <v>15.89894062306396</v>
       </c>
       <c r="D77">
-        <v>41.47851808441654</v>
+        <v>41.53094062306396</v>
       </c>
       <c r="E77">
-        <v>13.35</v>
+        <v>13.832</v>
       </c>
       <c r="F77">
-        <v>36.15000000000001</v>
+        <v>36.63200000000001</v>
       </c>
       <c r="G77">
         <v>11</v>
@@ -7601,28 +7601,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M77">
-        <v>2.215995</v>
+        <v>2.2455416</v>
       </c>
       <c r="N77">
-        <v>5.759004999999998</v>
+        <v>5.729458399999999</v>
       </c>
       <c r="O77">
-        <v>1.55493135</v>
+        <v>1.546953768</v>
       </c>
       <c r="P77">
-        <v>4.204073649999999</v>
+        <v>4.182504631999999</v>
       </c>
       <c r="Q77">
-        <v>7.904073649999999</v>
+        <v>7.882504631999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2025639779567719</v>
+        <v>0.2085429593521974</v>
       </c>
       <c r="T77">
-        <v>1.877992061691159</v>
+        <v>1.949618718171543</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.598834834916143</v>
+        <v>3.551481744983036</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08405955024452737</v>
+        <v>0.08391635599986175</v>
       </c>
       <c r="C78">
-        <v>15.89894062306396</v>
+        <v>15.46949583762604</v>
       </c>
       <c r="D78">
-        <v>41.53094062306396</v>
+        <v>41.58349583762605</v>
       </c>
       <c r="E78">
-        <v>13.832</v>
+        <v>14.314</v>
       </c>
       <c r="F78">
-        <v>36.63200000000001</v>
+        <v>37.114</v>
       </c>
       <c r="G78">
         <v>11</v>
@@ -7683,28 +7683,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M78">
-        <v>2.2455416</v>
+        <v>2.2750882</v>
       </c>
       <c r="N78">
-        <v>5.729458399999999</v>
+        <v>5.699911799999999</v>
       </c>
       <c r="O78">
-        <v>1.546953768</v>
+        <v>1.538976186</v>
       </c>
       <c r="P78">
-        <v>4.182504631999999</v>
+        <v>4.160935614</v>
       </c>
       <c r="Q78">
-        <v>7.882504631999999</v>
+        <v>7.860935614</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2085429593521974</v>
+        <v>0.215041852173312</v>
       </c>
       <c r="T78">
-        <v>1.949618718171543</v>
+        <v>2.027473779563264</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.551481744983036</v>
+        <v>3.505358605437801</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08391635599986175</v>
+        <v>0.08536748175519615</v>
       </c>
       <c r="C79">
-        <v>15.46949583762604</v>
+        <v>14.4609810831062</v>
       </c>
       <c r="D79">
-        <v>41.58349583762605</v>
+        <v>41.0569810831062</v>
       </c>
       <c r="E79">
-        <v>14.314</v>
+        <v>14.796</v>
       </c>
       <c r="F79">
-        <v>37.114</v>
+        <v>37.596</v>
       </c>
       <c r="G79">
         <v>11</v>
@@ -7765,45 +7765,45 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M79">
-        <v>2.2750882</v>
+        <v>2.4099036</v>
       </c>
       <c r="N79">
-        <v>5.699911799999999</v>
+        <v>5.565096399999998</v>
       </c>
       <c r="O79">
-        <v>1.538976186</v>
+        <v>1.502576028</v>
       </c>
       <c r="P79">
-        <v>4.160935614</v>
+        <v>4.062520371999998</v>
       </c>
       <c r="Q79">
-        <v>7.860935614</v>
+        <v>7.762520371999998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.215041852173312</v>
+        <v>0.2221315534327098</v>
       </c>
       <c r="T79">
-        <v>2.027473779563264</v>
+        <v>2.112406573808778</v>
       </c>
       <c r="U79">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V79">
         <v>0.27</v>
       </c>
       <c r="W79">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y79">
-        <v>3.505358605437801</v>
+        <v>3.309261001145439</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08536748175519615</v>
+        <v>0.08524472751053055</v>
       </c>
       <c r="C80">
-        <v>14.4609810831062</v>
+        <v>14.02300345540033</v>
       </c>
       <c r="D80">
-        <v>41.0569810831062</v>
+        <v>41.10100345540033</v>
       </c>
       <c r="E80">
-        <v>14.796</v>
+        <v>15.278</v>
       </c>
       <c r="F80">
-        <v>37.596</v>
+        <v>38.078</v>
       </c>
       <c r="G80">
         <v>11</v>
@@ -7847,28 +7847,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M80">
-        <v>2.4099036</v>
+        <v>2.4407998</v>
       </c>
       <c r="N80">
-        <v>5.565096399999998</v>
+        <v>5.534200199999999</v>
       </c>
       <c r="O80">
-        <v>1.502576028</v>
+        <v>1.494234054</v>
       </c>
       <c r="P80">
-        <v>4.062520371999998</v>
+        <v>4.039966145999999</v>
       </c>
       <c r="Q80">
-        <v>7.762520371999998</v>
+        <v>7.739966146</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2221315534327098</v>
+        <v>0.2298964643358598</v>
       </c>
       <c r="T80">
-        <v>2.112406573808778</v>
+        <v>2.205428205601485</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.309261001145439</v>
+        <v>3.267371621384105</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08524472751053055</v>
+        <v>0.08512197326586493</v>
       </c>
       <c r="C81">
-        <v>14.02300345540033</v>
+        <v>13.58512033291056</v>
       </c>
       <c r="D81">
-        <v>41.10100345540033</v>
+        <v>41.14512033291056</v>
       </c>
       <c r="E81">
-        <v>15.278</v>
+        <v>15.76</v>
       </c>
       <c r="F81">
-        <v>38.078</v>
+        <v>38.56</v>
       </c>
       <c r="G81">
         <v>11</v>
@@ -7929,28 +7929,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M81">
-        <v>2.4407998</v>
+        <v>2.471696</v>
       </c>
       <c r="N81">
-        <v>5.534200199999999</v>
+        <v>5.503303999999998</v>
       </c>
       <c r="O81">
-        <v>1.494234054</v>
+        <v>1.48589208</v>
       </c>
       <c r="P81">
-        <v>4.039966145999999</v>
+        <v>4.017411919999999</v>
       </c>
       <c r="Q81">
-        <v>7.739966146</v>
+        <v>7.717411919999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2298964643358598</v>
+        <v>0.2384378663293247</v>
       </c>
       <c r="T81">
-        <v>2.205428205601485</v>
+        <v>2.307752000573462</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.267371621384105</v>
+        <v>3.226529476116803</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08512197326586493</v>
+        <v>0.08499921902119933</v>
       </c>
       <c r="C82">
-        <v>13.58512033291056</v>
+        <v>13.14733202028307</v>
       </c>
       <c r="D82">
-        <v>41.14512033291056</v>
+        <v>41.18933202028307</v>
       </c>
       <c r="E82">
-        <v>15.76</v>
+        <v>16.242</v>
       </c>
       <c r="F82">
-        <v>38.56</v>
+        <v>39.042</v>
       </c>
       <c r="G82">
         <v>11</v>
@@ -8011,28 +8011,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M82">
-        <v>2.471696</v>
+        <v>2.5025922</v>
       </c>
       <c r="N82">
-        <v>5.503303999999998</v>
+        <v>5.472407799999999</v>
       </c>
       <c r="O82">
-        <v>1.48589208</v>
+        <v>1.477550106</v>
       </c>
       <c r="P82">
-        <v>4.017411919999999</v>
+        <v>3.994857693999999</v>
       </c>
       <c r="Q82">
-        <v>7.717411919999999</v>
+        <v>7.694857694</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2384378663293247</v>
+        <v>0.2478783632694702</v>
       </c>
       <c r="T82">
-        <v>2.307752000573462</v>
+        <v>2.420846721331962</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.226529476116803</v>
+        <v>3.186695778880794</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08499921902119933</v>
+        <v>0.08487646477653374</v>
       </c>
       <c r="C83">
-        <v>13.14733202028307</v>
+        <v>12.70963882347488</v>
       </c>
       <c r="D83">
-        <v>41.18933202028307</v>
+        <v>41.23363882347489</v>
       </c>
       <c r="E83">
-        <v>16.242</v>
+        <v>16.72400000000001</v>
       </c>
       <c r="F83">
-        <v>39.042</v>
+        <v>39.52400000000001</v>
       </c>
       <c r="G83">
         <v>11</v>
@@ -8093,28 +8093,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M83">
-        <v>2.5025922</v>
+        <v>2.533488400000001</v>
       </c>
       <c r="N83">
-        <v>5.472407799999999</v>
+        <v>5.441511599999998</v>
       </c>
       <c r="O83">
-        <v>1.477550106</v>
+        <v>1.469208132</v>
       </c>
       <c r="P83">
-        <v>3.994857693999999</v>
+        <v>3.972303467999999</v>
       </c>
       <c r="Q83">
-        <v>7.694857694</v>
+        <v>7.672303467999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2478783632694702</v>
+        <v>0.2583678043140764</v>
       </c>
       <c r="T83">
-        <v>2.420846721331962</v>
+        <v>2.546507522174741</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.186695778880794</v>
+        <v>3.147833635235905</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08487646477653374</v>
+        <v>0.08475371053186811</v>
       </c>
       <c r="C84">
-        <v>12.70963882347488</v>
+        <v>12.27204104976095</v>
       </c>
       <c r="D84">
-        <v>41.23363882347489</v>
+        <v>41.27804104976096</v>
       </c>
       <c r="E84">
-        <v>16.72400000000001</v>
+        <v>17.20600000000001</v>
       </c>
       <c r="F84">
-        <v>39.52400000000001</v>
+        <v>40.00600000000001</v>
       </c>
       <c r="G84">
         <v>11</v>
@@ -8175,28 +8175,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M84">
-        <v>2.533488400000001</v>
+        <v>2.564384600000001</v>
       </c>
       <c r="N84">
-        <v>5.441511599999998</v>
+        <v>5.410615399999998</v>
       </c>
       <c r="O84">
-        <v>1.469208132</v>
+        <v>1.460866158</v>
       </c>
       <c r="P84">
-        <v>3.972303467999999</v>
+        <v>3.949749241999998</v>
       </c>
       <c r="Q84">
-        <v>7.672303467999999</v>
+        <v>7.649749241999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2583678043140764</v>
+        <v>0.2700912972462832</v>
       </c>
       <c r="T84">
-        <v>2.546507522174741</v>
+        <v>2.686951946646083</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.147833635235905</v>
+        <v>3.109907928787279</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08475371053186811</v>
+        <v>0.08463095628720253</v>
       </c>
       <c r="C85">
-        <v>12.27204104976095</v>
+        <v>11.8345390077411</v>
       </c>
       <c r="D85">
-        <v>41.27804104976096</v>
+        <v>41.32253900774111</v>
       </c>
       <c r="E85">
-        <v>17.20600000000001</v>
+        <v>17.68800000000001</v>
       </c>
       <c r="F85">
-        <v>40.00600000000001</v>
+        <v>40.48800000000001</v>
       </c>
       <c r="G85">
         <v>11</v>
@@ -8257,28 +8257,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M85">
-        <v>2.564384600000001</v>
+        <v>2.595280800000001</v>
       </c>
       <c r="N85">
-        <v>5.410615399999998</v>
+        <v>5.379719199999998</v>
       </c>
       <c r="O85">
-        <v>1.460866158</v>
+        <v>1.452524184</v>
       </c>
       <c r="P85">
-        <v>3.949749241999998</v>
+        <v>3.927195015999999</v>
       </c>
       <c r="Q85">
-        <v>7.649749241999999</v>
+        <v>7.627195015999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2700912972462832</v>
+        <v>0.2832802267950159</v>
       </c>
       <c r="T85">
-        <v>2.686951946646083</v>
+        <v>2.844951924176342</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.109907928787279</v>
+        <v>3.072885215349336</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08463095628720252</v>
+        <v>0.08450820204253691</v>
       </c>
       <c r="C86">
-        <v>11.83453900774111</v>
+        <v>11.39713300734738</v>
       </c>
       <c r="D86">
-        <v>41.32253900774111</v>
+        <v>41.36713300734738</v>
       </c>
       <c r="E86">
-        <v>17.688</v>
+        <v>18.17</v>
       </c>
       <c r="F86">
-        <v>40.488</v>
+        <v>40.97</v>
       </c>
       <c r="G86">
         <v>11</v>
@@ -8339,28 +8339,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M86">
-        <v>2.5952808</v>
+        <v>2.626177</v>
       </c>
       <c r="N86">
-        <v>5.379719199999998</v>
+        <v>5.348822999999999</v>
       </c>
       <c r="O86">
-        <v>1.452524184</v>
+        <v>1.44418221</v>
       </c>
       <c r="P86">
-        <v>3.927195015999999</v>
+        <v>3.904640789999999</v>
       </c>
       <c r="Q86">
-        <v>7.627195015999999</v>
+        <v>7.604640789999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2832802267950157</v>
+        <v>0.2982276802835794</v>
       </c>
       <c r="T86">
-        <v>2.844951924176339</v>
+        <v>3.024018565377299</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.072885215349336</v>
+        <v>3.036733624580521</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08450820204253691</v>
+        <v>0.08438544779787131</v>
       </c>
       <c r="C87">
-        <v>11.39713300734738</v>
+        <v>10.95982335985108</v>
       </c>
       <c r="D87">
-        <v>41.36713300734738</v>
+        <v>41.41182335985108</v>
       </c>
       <c r="E87">
-        <v>18.17</v>
+        <v>18.652</v>
       </c>
       <c r="F87">
-        <v>40.97</v>
+        <v>41.45200000000001</v>
       </c>
       <c r="G87">
         <v>11</v>
@@ -8421,28 +8421,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M87">
-        <v>2.626177</v>
+        <v>2.657073200000001</v>
       </c>
       <c r="N87">
-        <v>5.348822999999999</v>
+        <v>5.317926799999999</v>
       </c>
       <c r="O87">
-        <v>1.44418221</v>
+        <v>1.435840236</v>
       </c>
       <c r="P87">
-        <v>3.904640789999999</v>
+        <v>3.882086563999999</v>
       </c>
       <c r="Q87">
-        <v>7.604640789999999</v>
+        <v>7.582086563999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2982276802835794</v>
+        <v>0.3153104842705093</v>
       </c>
       <c r="T87">
-        <v>3.024018565377299</v>
+        <v>3.228666155321253</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.036733624580521</v>
+        <v>3.001422768480747</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08438544779787131</v>
+        <v>0.08921647355320569</v>
       </c>
       <c r="C88">
-        <v>10.95982335985108</v>
+        <v>8.78892910922302</v>
       </c>
       <c r="D88">
-        <v>41.41182335985108</v>
+        <v>39.72292910922302</v>
       </c>
       <c r="E88">
-        <v>18.652</v>
+        <v>19.134</v>
       </c>
       <c r="F88">
-        <v>41.45200000000001</v>
+        <v>41.934</v>
       </c>
       <c r="G88">
         <v>11</v>
@@ -8503,45 +8503,45 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M88">
-        <v>2.657073200000001</v>
+        <v>3.0150546</v>
       </c>
       <c r="N88">
-        <v>5.317926799999999</v>
+        <v>4.959945399999999</v>
       </c>
       <c r="O88">
-        <v>1.435840236</v>
+        <v>1.339185258</v>
       </c>
       <c r="P88">
-        <v>3.882086563999999</v>
+        <v>3.620760141999999</v>
       </c>
       <c r="Q88">
-        <v>7.582086563999999</v>
+        <v>7.320760141999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3153104842705093</v>
+        <v>0.3350214119477361</v>
       </c>
       <c r="T88">
-        <v>3.228666155321253</v>
+        <v>3.464797989871968</v>
       </c>
       <c r="U88">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V88">
         <v>0.27</v>
       </c>
       <c r="W88">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>3.001422768480747</v>
+        <v>2.645059893774394</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08921647355320569</v>
+        <v>0.0891506593085401</v>
       </c>
       <c r="C89">
-        <v>8.78892910922302</v>
+        <v>8.329011255236715</v>
       </c>
       <c r="D89">
-        <v>39.72292910922302</v>
+        <v>39.74501125523672</v>
       </c>
       <c r="E89">
-        <v>19.134</v>
+        <v>19.616</v>
       </c>
       <c r="F89">
-        <v>41.934</v>
+        <v>42.416</v>
       </c>
       <c r="G89">
         <v>11</v>
@@ -8585,28 +8585,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M89">
-        <v>3.0150546</v>
+        <v>3.0497104</v>
       </c>
       <c r="N89">
-        <v>4.959945399999999</v>
+        <v>4.925289599999998</v>
       </c>
       <c r="O89">
-        <v>1.339185258</v>
+        <v>1.329828192</v>
       </c>
       <c r="P89">
-        <v>3.620760141999999</v>
+        <v>3.595461407999998</v>
       </c>
       <c r="Q89">
-        <v>7.320760141999999</v>
+        <v>7.295461407999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3350214119477361</v>
+        <v>0.3580174942378341</v>
       </c>
       <c r="T89">
-        <v>3.464797989871968</v>
+        <v>3.740285130181138</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.645059893774394</v>
+        <v>2.615002394981503</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0891506593085401</v>
+        <v>0.0890848450638745</v>
       </c>
       <c r="C90">
-        <v>8.329011255236715</v>
+        <v>7.86911796602471</v>
       </c>
       <c r="D90">
-        <v>39.74501125523672</v>
+        <v>39.76711796602471</v>
       </c>
       <c r="E90">
-        <v>19.616</v>
+        <v>20.098</v>
       </c>
       <c r="F90">
-        <v>42.416</v>
+        <v>42.898</v>
       </c>
       <c r="G90">
         <v>11</v>
@@ -8667,28 +8667,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M90">
-        <v>3.0497104</v>
+        <v>3.0843662</v>
       </c>
       <c r="N90">
-        <v>4.925289599999998</v>
+        <v>4.890633799999998</v>
       </c>
       <c r="O90">
-        <v>1.329828192</v>
+        <v>1.320471125999999</v>
       </c>
       <c r="P90">
-        <v>3.595461407999998</v>
+        <v>3.570162673999999</v>
       </c>
       <c r="Q90">
-        <v>7.295461407999999</v>
+        <v>7.270162673999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3580174942378341</v>
+        <v>0.3851946823988591</v>
       </c>
       <c r="T90">
-        <v>3.740285130181138</v>
+        <v>4.06586084145561</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.615002394981503</v>
+        <v>2.585620345599688</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.0890848450638745</v>
+        <v>0.08901903081920888</v>
       </c>
       <c r="C91">
-        <v>7.86911796602471</v>
+        <v>7.409249282599603</v>
       </c>
       <c r="D91">
-        <v>39.76711796602471</v>
+        <v>39.78924928259961</v>
       </c>
       <c r="E91">
-        <v>20.098</v>
+        <v>20.58</v>
       </c>
       <c r="F91">
-        <v>42.898</v>
+        <v>43.38</v>
       </c>
       <c r="G91">
         <v>11</v>
@@ -8749,28 +8749,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M91">
-        <v>3.0843662</v>
+        <v>3.119022000000001</v>
       </c>
       <c r="N91">
-        <v>4.890633799999998</v>
+        <v>4.855977999999999</v>
       </c>
       <c r="O91">
-        <v>1.320471125999999</v>
+        <v>1.31111406</v>
       </c>
       <c r="P91">
-        <v>3.570162673999999</v>
+        <v>3.544863939999999</v>
       </c>
       <c r="Q91">
-        <v>7.270162673999999</v>
+        <v>7.244863939999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3851946823988591</v>
+        <v>0.4178073081920888</v>
       </c>
       <c r="T91">
-        <v>4.06586084145561</v>
+        <v>4.456551694984975</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.585620345599688</v>
+        <v>2.55689123064858</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08901903081920888</v>
+        <v>0.08895321657454328</v>
       </c>
       <c r="C92">
-        <v>7.409249282599603</v>
+        <v>6.949405246065304</v>
       </c>
       <c r="D92">
-        <v>39.78924928259961</v>
+        <v>39.81140524606531</v>
       </c>
       <c r="E92">
-        <v>20.58</v>
+        <v>21.062</v>
       </c>
       <c r="F92">
-        <v>43.38</v>
+        <v>43.862</v>
       </c>
       <c r="G92">
         <v>11</v>
@@ -8831,28 +8831,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M92">
-        <v>3.119022000000001</v>
+        <v>3.153677800000001</v>
       </c>
       <c r="N92">
-        <v>4.855977999999999</v>
+        <v>4.821322199999998</v>
       </c>
       <c r="O92">
-        <v>1.31111406</v>
+        <v>1.301756994</v>
       </c>
       <c r="P92">
-        <v>3.544863939999999</v>
+        <v>3.519565205999998</v>
       </c>
       <c r="Q92">
-        <v>7.244863939999999</v>
+        <v>7.219565205999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4178073081920888</v>
+        <v>0.4576671841615921</v>
       </c>
       <c r="T92">
-        <v>4.456551694984975</v>
+        <v>4.934062738187535</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.55689123064858</v>
+        <v>2.528793524817278</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08895321657454328</v>
+        <v>0.08888740232987766</v>
       </c>
       <c r="C93">
-        <v>6.949405246065304</v>
+        <v>6.489585897617374</v>
       </c>
       <c r="D93">
-        <v>39.81140524606531</v>
+        <v>39.83358589761738</v>
       </c>
       <c r="E93">
-        <v>21.062</v>
+        <v>21.544</v>
       </c>
       <c r="F93">
-        <v>43.862</v>
+        <v>44.344</v>
       </c>
       <c r="G93">
         <v>11</v>
@@ -8913,28 +8913,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M93">
-        <v>3.153677800000001</v>
+        <v>3.1883336</v>
       </c>
       <c r="N93">
-        <v>4.821322199999998</v>
+        <v>4.786666399999998</v>
       </c>
       <c r="O93">
-        <v>1.301756994</v>
+        <v>1.292399928</v>
       </c>
       <c r="P93">
-        <v>3.519565205999998</v>
+        <v>3.494266471999998</v>
       </c>
       <c r="Q93">
-        <v>7.219565205999999</v>
+        <v>7.194266471999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4576671841615921</v>
+        <v>0.507492029123471</v>
       </c>
       <c r="T93">
-        <v>4.934062738187535</v>
+        <v>5.530951542190735</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.528793524817278</v>
+        <v>2.501306638677959</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08888740232987766</v>
+        <v>0.09146929808521206</v>
       </c>
       <c r="C94">
-        <v>6.489585897617374</v>
+        <v>5.155575332717341</v>
       </c>
       <c r="D94">
-        <v>39.83358589761738</v>
+        <v>38.98157533271735</v>
       </c>
       <c r="E94">
-        <v>21.544</v>
+        <v>22.02600000000001</v>
       </c>
       <c r="F94">
-        <v>44.344</v>
+        <v>44.82600000000001</v>
       </c>
       <c r="G94">
         <v>11</v>
@@ -8995,45 +8995,45 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M94">
-        <v>3.1883336</v>
+        <v>3.397810800000001</v>
       </c>
       <c r="N94">
-        <v>4.786666399999998</v>
+        <v>4.577189199999998</v>
       </c>
       <c r="O94">
-        <v>1.292399928</v>
+        <v>1.235841083999999</v>
       </c>
       <c r="P94">
-        <v>3.494266471999998</v>
+        <v>3.341348115999998</v>
       </c>
       <c r="Q94">
-        <v>7.194266471999999</v>
+        <v>7.041348115999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.507492029123471</v>
+        <v>0.5715525440744583</v>
       </c>
       <c r="T94">
-        <v>5.530951542190735</v>
+        <v>6.298380004480562</v>
       </c>
       <c r="U94">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V94">
         <v>0.27</v>
       </c>
       <c r="W94">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y94">
-        <v>2.501306638677959</v>
+        <v>2.347099491237121</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09146929808521206</v>
+        <v>0.09143195384054645</v>
       </c>
       <c r="C95">
-        <v>5.155575332717341</v>
+        <v>4.685638860177868</v>
       </c>
       <c r="D95">
-        <v>38.98157533271735</v>
+        <v>38.99363886017787</v>
       </c>
       <c r="E95">
-        <v>22.02600000000001</v>
+        <v>22.50800000000001</v>
       </c>
       <c r="F95">
-        <v>44.82600000000001</v>
+        <v>45.30800000000001</v>
       </c>
       <c r="G95">
         <v>11</v>
@@ -9077,28 +9077,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M95">
-        <v>3.397810800000001</v>
+        <v>3.434346400000001</v>
       </c>
       <c r="N95">
-        <v>4.577189199999998</v>
+        <v>4.540653599999998</v>
       </c>
       <c r="O95">
-        <v>1.235841083999999</v>
+        <v>1.225976471999999</v>
       </c>
       <c r="P95">
-        <v>3.341348115999998</v>
+        <v>3.314677127999999</v>
       </c>
       <c r="Q95">
-        <v>7.041348115999998</v>
+        <v>7.014677127999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5715525440744583</v>
+        <v>0.6569665640091081</v>
       </c>
       <c r="T95">
-        <v>6.298380004480562</v>
+        <v>7.321617954200334</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.347099491237121</v>
+        <v>2.322130347713323</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09143195384054645</v>
+        <v>0.09139460959588086</v>
       </c>
       <c r="C96">
-        <v>4.685638860177868</v>
+        <v>4.21570985648713</v>
       </c>
       <c r="D96">
-        <v>38.99363886017787</v>
+        <v>39.00570985648714</v>
       </c>
       <c r="E96">
-        <v>22.50800000000001</v>
+        <v>22.99000000000001</v>
       </c>
       <c r="F96">
-        <v>45.30800000000001</v>
+        <v>45.79000000000001</v>
       </c>
       <c r="G96">
         <v>11</v>
@@ -9159,28 +9159,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M96">
-        <v>3.434346400000001</v>
+        <v>3.470882000000001</v>
       </c>
       <c r="N96">
-        <v>4.540653599999998</v>
+        <v>4.504117999999998</v>
       </c>
       <c r="O96">
-        <v>1.225976471999999</v>
+        <v>1.21611186</v>
       </c>
       <c r="P96">
-        <v>3.314677127999999</v>
+        <v>3.288006139999998</v>
       </c>
       <c r="Q96">
-        <v>7.014677127999999</v>
+        <v>6.988006139999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6569665640091081</v>
+        <v>0.776546191917618</v>
       </c>
       <c r="T96">
-        <v>7.321617954200334</v>
+        <v>8.754151083808015</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.322130347713323</v>
+        <v>2.297686870368972</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09139460959588086</v>
+        <v>0.09135726535121524</v>
       </c>
       <c r="C97">
-        <v>4.21570985648713</v>
+        <v>3.745788328583544</v>
       </c>
       <c r="D97">
-        <v>39.00570985648714</v>
+        <v>39.01778832858355</v>
       </c>
       <c r="E97">
-        <v>22.99000000000001</v>
+        <v>23.472</v>
       </c>
       <c r="F97">
-        <v>45.79000000000001</v>
+        <v>46.27200000000001</v>
       </c>
       <c r="G97">
         <v>11</v>
@@ -9241,28 +9241,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M97">
-        <v>3.470882000000001</v>
+        <v>3.507417600000001</v>
       </c>
       <c r="N97">
-        <v>4.504117999999998</v>
+        <v>4.467582399999998</v>
       </c>
       <c r="O97">
-        <v>1.21611186</v>
+        <v>1.206247247999999</v>
       </c>
       <c r="P97">
-        <v>3.288006139999998</v>
+        <v>3.261335151999998</v>
       </c>
       <c r="Q97">
-        <v>6.988006139999999</v>
+        <v>6.961335151999998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.776546191917618</v>
+        <v>0.9559156337803826</v>
       </c>
       <c r="T97">
-        <v>8.754151083808015</v>
+        <v>10.90295077821954</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.297686870368972</v>
+        <v>2.273752632135961</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09135726535121524</v>
+        <v>0.09131992110654964</v>
       </c>
       <c r="C98">
-        <v>3.745788328583551</v>
+        <v>3.275874283414076</v>
       </c>
       <c r="D98">
-        <v>39.01778832858355</v>
+        <v>39.02987428341408</v>
       </c>
       <c r="E98">
-        <v>23.472</v>
+        <v>23.954</v>
       </c>
       <c r="F98">
-        <v>46.272</v>
+        <v>46.754</v>
       </c>
       <c r="G98">
         <v>11</v>
@@ -9323,28 +9323,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M98">
-        <v>3.5074176</v>
+        <v>3.543953200000001</v>
       </c>
       <c r="N98">
-        <v>4.467582399999999</v>
+        <v>4.431046799999998</v>
       </c>
       <c r="O98">
-        <v>1.206247248</v>
+        <v>1.196382636</v>
       </c>
       <c r="P98">
-        <v>3.261335151999999</v>
+        <v>3.234664163999998</v>
       </c>
       <c r="Q98">
-        <v>6.961335151999999</v>
+        <v>6.934664163999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9559156337803802</v>
+        <v>1.254864703551654</v>
       </c>
       <c r="T98">
-        <v>10.90295077821951</v>
+        <v>14.48428360223869</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.273752632135962</v>
+        <v>2.250311883351054</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09131992110654964</v>
+        <v>0.09128257686188404</v>
       </c>
       <c r="C99">
-        <v>3.275874283414076</v>
+        <v>2.805967727934345</v>
       </c>
       <c r="D99">
-        <v>39.02987428341408</v>
+        <v>39.04196772793435</v>
       </c>
       <c r="E99">
-        <v>23.954</v>
+        <v>24.436</v>
       </c>
       <c r="F99">
-        <v>46.754</v>
+        <v>47.236</v>
       </c>
       <c r="G99">
         <v>11</v>
@@ -9405,28 +9405,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M99">
-        <v>3.543953200000001</v>
+        <v>3.580488800000001</v>
       </c>
       <c r="N99">
-        <v>4.431046799999998</v>
+        <v>4.394511199999998</v>
       </c>
       <c r="O99">
-        <v>1.196382636</v>
+        <v>1.186518024</v>
       </c>
       <c r="P99">
-        <v>3.234664163999998</v>
+        <v>3.207993175999999</v>
       </c>
       <c r="Q99">
-        <v>6.934664163999999</v>
+        <v>6.907993175999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.254864703551654</v>
+        <v>1.8527628430942</v>
       </c>
       <c r="T99">
-        <v>14.48428360223869</v>
+        <v>21.64694925027707</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.250311883351054</v>
+        <v>2.227349517194411</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09128257686188404</v>
+        <v>0.09124523261721842</v>
       </c>
       <c r="C100">
-        <v>2.805967727934345</v>
+        <v>2.336068669108556</v>
       </c>
       <c r="D100">
-        <v>39.04196772793435</v>
+        <v>39.05406866910856</v>
       </c>
       <c r="E100">
-        <v>24.436</v>
+        <v>24.918</v>
       </c>
       <c r="F100">
-        <v>47.236</v>
+        <v>47.718</v>
       </c>
       <c r="G100">
         <v>11</v>
@@ -9487,28 +9487,28 @@
         <v>7.974999999999999</v>
       </c>
       <c r="M100">
-        <v>3.580488800000001</v>
+        <v>3.6170244</v>
       </c>
       <c r="N100">
-        <v>4.394511199999998</v>
+        <v>4.357975599999998</v>
       </c>
       <c r="O100">
-        <v>1.186518024</v>
+        <v>1.176653411999999</v>
       </c>
       <c r="P100">
-        <v>3.207993175999999</v>
+        <v>3.181322187999998</v>
       </c>
       <c r="Q100">
-        <v>6.907993175999999</v>
+        <v>6.881322187999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.8527628430942</v>
+        <v>3.646457261721839</v>
       </c>
       <c r="T100">
-        <v>21.64694925027707</v>
+        <v>43.13494619439219</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.227349517194411</v>
+        <v>2.204851037222751</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09124523261721842</v>
-      </c>
-      <c r="C101">
-        <v>2.336068669108556</v>
-      </c>
-      <c r="D101">
-        <v>39.05406866910856</v>
-      </c>
-      <c r="E101">
-        <v>24.918</v>
-      </c>
-      <c r="F101">
-        <v>47.718</v>
-      </c>
-      <c r="G101">
-        <v>11</v>
-      </c>
-      <c r="H101">
-        <v>25.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>11.675</v>
-      </c>
-      <c r="K101">
-        <v>3.7</v>
-      </c>
-      <c r="L101">
-        <v>7.974999999999999</v>
-      </c>
-      <c r="M101">
-        <v>3.6170244</v>
-      </c>
-      <c r="N101">
-        <v>4.357975599999998</v>
-      </c>
-      <c r="O101">
-        <v>1.176653411999999</v>
-      </c>
-      <c r="P101">
-        <v>3.181322187999998</v>
-      </c>
-      <c r="Q101">
-        <v>6.881322187999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.646457261721839</v>
-      </c>
-      <c r="T101">
-        <v>43.13494619439219</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.27</v>
-      </c>
-      <c r="W101">
-        <v>0.055334</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.204851037222751</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
